--- a/format-laporan/hari-minggu-2026/Format Baru Permen 6 2026 (1) (1)/Fix/00 Database.xlsx
+++ b/format-laporan/hari-minggu-2026/Format Baru Permen 6 2026 (1) (1)/Fix/00 Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/febri/Library/Mobile Documents/com~apple~CloudDocs/Downloads/BP3KP Papua II/2026/01 BSPS/Format BSPS Papua II/Format Baru Permen 6 2026/Fix/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSPS-2026\format-laporan\hari-minggu-2026\Format Baru Permen 6 2026 (1) (1)\Fix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4401AE2-4028-BF4E-8A9A-E30A63231B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D132E7-43B5-4C61-8827-008C0A10B17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="16800" windowHeight="19260" activeTab="1" xr2:uid="{F26A00DE-12D0-554C-ABD8-D44599DA1687}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{F26A00DE-12D0-554C-ABD8-D44599DA1687}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_01" sheetId="1" r:id="rId1"/>
@@ -40,8 +40,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -143,15 +141,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="184">
-  <si>
-    <t>Klasabi</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="193">
   <si>
     <t>Distrik</t>
-  </si>
-  <si>
-    <t>Sorong Manoi</t>
   </si>
   <si>
     <t>Sorong</t>
@@ -172,16 +164,10 @@
     <t>Nilai Bantuan</t>
   </si>
   <si>
-    <t>Kelurahan</t>
-  </si>
-  <si>
     <t>Kota</t>
   </si>
   <si>
     <t>NIP ….......................................</t>
-  </si>
-  <si>
-    <t>Jl Desa Karya ………</t>
   </si>
   <si>
     <t>Alamat Kantor</t>
@@ -211,13 +197,7 @@
     <t>NIP 199702092020121005</t>
   </si>
   <si>
-    <t>AfrIandi Yudhistira, S.T.</t>
-  </si>
-  <si>
     <t>…...............</t>
-  </si>
-  <si>
-    <t>Arnold Howay</t>
   </si>
   <si>
     <t>TPM Teknik</t>
@@ -307,9 +287,6 @@
     <t>Penamaan Folder</t>
   </si>
   <si>
-    <t>000001</t>
-  </si>
-  <si>
     <t>Mengurus Rumah Tangga</t>
   </si>
   <si>
@@ -337,9 +314,6 @@
     <t xml:space="preserve"> Tahun</t>
   </si>
   <si>
-    <t>000002</t>
-  </si>
-  <si>
     <t>Petani</t>
   </si>
   <si>
@@ -361,9 +335,6 @@
     <t>Barat 2</t>
   </si>
   <si>
-    <t>000003</t>
-  </si>
-  <si>
     <t>Buruh</t>
   </si>
   <si>
@@ -380,9 +351,6 @@
   </si>
   <si>
     <t>Barat 3</t>
-  </si>
-  <si>
-    <t>000004</t>
   </si>
   <si>
     <t>Wiraswasta</t>
@@ -403,9 +371,6 @@
     <t>Barat 4</t>
   </si>
   <si>
-    <t>000005</t>
-  </si>
-  <si>
     <t>Buruh Harian Lepas</t>
   </si>
   <si>
@@ -424,9 +389,6 @@
     <t>Barat 5</t>
   </si>
   <si>
-    <t>000006</t>
-  </si>
-  <si>
     <t>3304160101850004</t>
   </si>
   <si>
@@ -440,9 +402,6 @@
   </si>
   <si>
     <t>Barat 6</t>
-  </si>
-  <si>
-    <t>000007</t>
   </si>
   <si>
     <t>3304160101860004</t>
@@ -565,30 +524,6 @@
     <t>Gambar Rencana Teknis</t>
   </si>
   <si>
-    <t>Nama PB 1</t>
-  </si>
-  <si>
-    <t>Nama PB 2</t>
-  </si>
-  <si>
-    <t>Nama PB 3</t>
-  </si>
-  <si>
-    <t>Nama PB 4</t>
-  </si>
-  <si>
-    <t>Nama PB 5</t>
-  </si>
-  <si>
-    <t>Nama PB 6</t>
-  </si>
-  <si>
-    <t>Nama PB 7</t>
-  </si>
-  <si>
-    <t>Nama PB 8</t>
-  </si>
-  <si>
     <t>Nama PB 9</t>
   </si>
   <si>
@@ -623,9 +558,6 @@
   </si>
   <si>
     <t>Nama PB 20</t>
-  </si>
-  <si>
-    <t>000008</t>
   </si>
   <si>
     <t>000009</t>
@@ -697,17 +629,110 @@
   <si>
     <t>Sekolah Menengah Atas</t>
   </si>
+  <si>
+    <t>Kampung</t>
+  </si>
+  <si>
+    <t>Wayane</t>
+  </si>
+  <si>
+    <t>Aifat Utara</t>
+  </si>
+  <si>
+    <t>92.10.02.2007</t>
+  </si>
+  <si>
+    <t>Paskalis Korain</t>
+  </si>
+  <si>
+    <t>Kampung Wayane</t>
+  </si>
+  <si>
+    <t>Amos Jitmau, S.T</t>
+  </si>
+  <si>
+    <t>Paulus Sesa, S.Kom</t>
+  </si>
+  <si>
+    <t>23, September 2026</t>
+  </si>
+  <si>
+    <t>25, September  2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGNES ASSEM </t>
+  </si>
+  <si>
+    <t>96050450</t>
+  </si>
+  <si>
+    <t>96050451</t>
+  </si>
+  <si>
+    <t>96050452</t>
+  </si>
+  <si>
+    <t>96050453</t>
+  </si>
+  <si>
+    <t>96050457</t>
+  </si>
+  <si>
+    <t>96050458</t>
+  </si>
+  <si>
+    <t>96050460</t>
+  </si>
+  <si>
+    <t>96050464</t>
+  </si>
+  <si>
+    <t>AKNES KORAIN</t>
+  </si>
+  <si>
+    <t>APOLONIA KORAIN</t>
+  </si>
+  <si>
+    <t>BARTOLOMEUS KORAIN</t>
+  </si>
+  <si>
+    <t>MATILDA TAA</t>
+  </si>
+  <si>
+    <t>MONICA KORAIN</t>
+  </si>
+  <si>
+    <t>PASKALIS YUMTE</t>
+  </si>
+  <si>
+    <t>WIHELMUS KORAIN</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAMAT </t>
+  </si>
+  <si>
+    <t>MOSUN</t>
+  </si>
+  <si>
+    <t>AIFAT</t>
+  </si>
+  <si>
+    <t>SABES</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="42" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="@\ * \:"/>
-    <numFmt numFmtId="165" formatCode="[$-13809]d\ mmm\ yyyy;@"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="@\ * \:"/>
+    <numFmt numFmtId="167" formatCode="[$-13809]d\ mmm\ yyyy;@"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -944,15 +969,15 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -974,7 +999,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1004,7 +1029,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="13" fillId="4" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1051,7 +1076,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1077,7 +1102,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1113,25 +1138,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1178,7 +1203,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1192,12 +1217,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{E09FD1F8-35A6-454A-B7B2-8D124FC4FCA3}"/>
@@ -1205,6 +1238,16 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7589842B-B365-B946-A563-BCB40ACE3300}"/>
   </cellStyles>
   <dxfs count="26">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1240,6 +1283,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1295,13 +1345,9 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -1309,9 +1355,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -1443,16 +1486,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1469,6 +1502,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Indeks"/>
       <sheetName val="Data Umum"/>
@@ -48373,7 +48409,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="B2:F29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34.33203125" style="1" customWidth="1"/>
@@ -48381,221 +48417,222 @@
     <col min="4" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B2" s="56" t="s">
-        <v>9</v>
+        <v>162</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" s="58" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>2</v>
+        <v>164</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="1" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" s="56" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" s="57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B5" s="58" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="65" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B5" s="58" t="s">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B6" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C6" s="59">
+        <v>98277</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B7" s="58" t="s">
         <v>5</v>
       </c>
+      <c r="C7" s="57" t="s">
+        <v>165</v>
+      </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B6" s="58" t="s">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B8" s="58" t="s">
         <v>6</v>
-      </c>
-      <c r="C6" s="59"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B7" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="57"/>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B8" s="58" t="s">
-        <v>8</v>
       </c>
       <c r="C8" s="60">
         <v>40000000</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" s="58" t="str">
         <f>"Nama Kepala "&amp;B2</f>
-        <v>Nama Kepala Kelurahan</v>
+        <v>Nama Kepala Kampung</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" s="58" t="str">
         <f>"NIP "&amp;F24</f>
         <v xml:space="preserve">NIP </v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" s="58" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>12</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" s="58" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C12" s="61">
         <v>3766000</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" s="58" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C13" s="61">
         <v>3766000</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="45" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:6" ht="42" x14ac:dyDescent="0.35">
       <c r="B14" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="62" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B15" s="58" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="63" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="62" t="s">
-        <v>19</v>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B16" s="58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="63" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B15" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="63" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B16" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="63" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B17" s="58" t="str">
         <f>"Koordinator "&amp;B4</f>
         <v>Koordinator Kota</v>
       </c>
       <c r="C17" s="63" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B18" s="58" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B19" s="58" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>23</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B20" s="64"/>
-      <c r="C20" s="24" t="str">
-        <f>C18&amp;"         " &amp; C19</f>
-        <v>…...............         …...............</v>
+      <c r="C20" s="24"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="s">
-        <v>117</v>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B26" s="58" t="s">
+        <v>103</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>118</v>
+      <c r="C26" s="57" t="s">
+        <v>170</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>119</v>
+      <c r="D26" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="58" t="s">
-        <v>116</v>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B27" s="58" t="s">
+        <v>124</v>
       </c>
-      <c r="C26" s="57" t="s">
-        <v>136</v>
+      <c r="C27" s="57" t="s">
+        <v>170</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>120</v>
+      <c r="D27" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B27" s="58" t="s">
-        <v>137</v>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B28" s="58" t="s">
+        <v>126</v>
       </c>
-      <c r="C27" s="57" t="s">
-        <v>136</v>
+      <c r="C28" s="57" t="s">
+        <v>123</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>138</v>
+      <c r="D28" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="58" t="s">
-        <v>139</v>
-      </c>
-      <c r="C28" s="57" t="s">
-        <v>136</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B29" s="58" t="s">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="4">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 E2" xr:uid="{369A336D-9BD5-6B4A-B795-06F2803E6F63}">
       <formula1>"Kampung,Kelurahan"</formula1>
     </dataValidation>
@@ -48620,7 +48657,7 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:AL35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.83203125" style="26" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" style="26" customWidth="1"/>
@@ -48651,7 +48688,7 @@
     <col min="39" max="16384" width="9.1640625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:38" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="25"/>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -48665,111 +48702,111 @@
       <c r="K1" s="25"/>
       <c r="L1" s="25"/>
     </row>
-    <row r="2" spans="1:38" s="27" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" s="27" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="79" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="79" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="I2" s="73" t="s">
+        <v>108</v>
+      </c>
+      <c r="J2" s="73" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="74" t="s">
+      <c r="K2" s="73" t="s">
         <v>29</v>
-      </c>
-      <c r="E2" s="74" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="74" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="73" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="73" t="s">
-        <v>121</v>
-      </c>
-      <c r="J2" s="73" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="73" t="s">
-        <v>35</v>
       </c>
       <c r="L2" s="73"/>
       <c r="M2" s="73"/>
       <c r="N2" s="73" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="O2" s="75" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P2" s="73" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Q2" s="75" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R2" s="73" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="S2" s="73"/>
       <c r="T2" s="73" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="U2" s="73"/>
       <c r="V2" s="73"/>
       <c r="W2" s="73"/>
       <c r="X2" s="73" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Y2" s="73"/>
       <c r="Z2" s="73"/>
       <c r="AA2" s="75" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="AB2" s="75" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="AC2" s="75" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="AD2" s="75" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="AE2" s="73" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
-      <c r="AF2" s="80" t="s">
-        <v>178</v>
+      <c r="AF2" s="74" t="s">
+        <v>156</v>
       </c>
       <c r="AG2" s="73" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="AH2" s="29"/>
     </row>
-    <row r="3" spans="1:38" s="27" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:38" s="27" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="73"/>
       <c r="B3" s="73"/>
       <c r="C3" s="73"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
       <c r="H3" s="73"/>
       <c r="I3" s="73"/>
       <c r="J3" s="73"/>
       <c r="K3" s="73" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="L3" s="73" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M3" s="73" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="N3" s="73"/>
       <c r="O3" s="76"/>
@@ -48778,16 +48815,16 @@
       <c r="R3" s="73"/>
       <c r="S3" s="73"/>
       <c r="T3" s="73" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="U3" s="73" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="V3" s="73" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="W3" s="73" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="X3" s="73"/>
       <c r="Y3" s="73"/>
@@ -48797,18 +48834,18 @@
       <c r="AC3" s="76"/>
       <c r="AD3" s="76"/>
       <c r="AE3" s="73"/>
-      <c r="AF3" s="80"/>
+      <c r="AF3" s="74"/>
       <c r="AG3" s="73"/>
       <c r="AH3" s="29"/>
     </row>
-    <row r="4" spans="1:38" s="27" customFormat="1" ht="41.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:38" s="27" customFormat="1" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="73"/>
       <c r="B4" s="73"/>
       <c r="C4" s="73"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
       <c r="H4" s="73"/>
       <c r="I4" s="73"/>
       <c r="J4" s="73"/>
@@ -48826,61 +48863,61 @@
       <c r="V4" s="73"/>
       <c r="W4" s="73"/>
       <c r="X4" s="28" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y4" s="28" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="Z4" s="28" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="AA4" s="77"/>
       <c r="AB4" s="77"/>
       <c r="AC4" s="77"/>
       <c r="AD4" s="77"/>
       <c r="AE4" s="73"/>
-      <c r="AF4" s="80"/>
+      <c r="AF4" s="74"/>
       <c r="AG4" s="73"/>
       <c r="AH4" s="29"/>
       <c r="AI4" s="28" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="AK4" s="29"/>
     </row>
-    <row r="5" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="30">
         <v>1</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>54</v>
+      <c r="B5" s="81" t="s">
+        <v>173</v>
       </c>
-      <c r="C5" s="32" t="s">
-        <v>140</v>
+      <c r="C5" s="82" t="s">
+        <v>172</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>51</v>
+      <c r="D5" s="83" t="s">
+        <v>44</v>
       </c>
-      <c r="E5" s="34" t="s">
-        <v>3</v>
+      <c r="E5" s="82" t="s">
+        <v>189</v>
       </c>
-      <c r="F5" s="35">
-        <v>36526</v>
+      <c r="F5" s="84">
+        <v>23478</v>
       </c>
       <c r="G5" s="36">
         <f ca="1">INT((TODAY()-F5)/365)</f>
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I5" s="67" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K5" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L5" s="39">
         <v>1</v>
@@ -48889,14 +48926,14 @@
         <v>1</v>
       </c>
       <c r="N5" s="72" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="O5" s="41">
         <f>LEN(N5)</f>
         <v>16</v>
       </c>
       <c r="P5" s="40" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="Q5" s="41">
         <f>LEN(P5)</f>
@@ -48909,16 +48946,16 @@
         <v>109.5536</v>
       </c>
       <c r="T5" s="43" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="U5" s="43" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="V5" s="43" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="W5" s="43" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="X5" s="44">
         <v>1</v>
@@ -48931,73 +48968,73 @@
         <v>10</v>
       </c>
       <c r="AA5" s="44" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="AB5" s="69" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="AC5" s="44" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="AD5" s="69">
         <v>2020</v>
       </c>
       <c r="AE5" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF5" s="70">
         <v>1600006544205</v>
       </c>
       <c r="AG5" s="69" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="AH5" s="45"/>
       <c r="AI5" s="46" t="str">
         <f>B5&amp;AF5&amp;C5</f>
-        <v>0000011600006544205Nama PB 1</v>
+        <v xml:space="preserve">960504501600006544205AGNES ASSEM </v>
       </c>
       <c r="AK5" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL5" s="25" t="str">
         <f t="shared" ref="AL5:AL24" ca="1" si="0">G5&amp;AK5</f>
-        <v>26 Tahun</v>
+        <v>62 Tahun</v>
       </c>
     </row>
-    <row r="6" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="47">
         <v>2</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>64</v>
+      <c r="B6" s="81" t="s">
+        <v>174</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>141</v>
+      <c r="C6" s="82" t="s">
+        <v>181</v>
       </c>
-      <c r="D6" s="33" t="s">
-        <v>51</v>
+      <c r="D6" s="83" t="s">
+        <v>44</v>
       </c>
-      <c r="E6" s="34" t="s">
-        <v>3</v>
+      <c r="E6" s="82" t="s">
+        <v>190</v>
       </c>
-      <c r="F6" s="35">
-        <v>36526</v>
+      <c r="F6" s="84">
+        <v>21002</v>
       </c>
       <c r="G6" s="36">
         <f t="shared" ref="G6:G11" ca="1" si="1">INT((TODAY()-F6)/365)</f>
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="H6" s="48" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="I6" s="67" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L6" s="39">
         <v>1</v>
@@ -49006,14 +49043,14 @@
         <v>1</v>
       </c>
       <c r="N6" s="40" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="O6" s="41">
         <f t="shared" ref="O6:Q11" si="2">LEN(N6)</f>
         <v>16</v>
       </c>
       <c r="P6" s="40" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="Q6" s="41">
         <f t="shared" si="2"/>
@@ -49026,16 +49063,16 @@
         <v>109.5594</v>
       </c>
       <c r="T6" s="43" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="U6" s="43" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="V6" s="43" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="W6" s="43" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="X6" s="44">
         <v>2</v>
@@ -49048,67 +49085,67 @@
         <v>20</v>
       </c>
       <c r="AA6" s="44" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="AB6" s="69"/>
       <c r="AC6" s="44"/>
       <c r="AD6" s="69"/>
       <c r="AE6" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF6" s="70">
         <v>1600006544213</v>
       </c>
       <c r="AG6" s="69" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="AH6" s="45"/>
       <c r="AI6" s="46" t="str">
         <f t="shared" ref="AI6:AI24" si="4">B6&amp;AF6&amp;C6</f>
-        <v>0000021600006544213Nama PB 2</v>
+        <v>960504511600006544213AKNES KORAIN</v>
       </c>
       <c r="AK6" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL6" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>26 Tahun</v>
+        <v>69 Tahun</v>
       </c>
     </row>
-    <row r="7" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="47">
         <v>3</v>
       </c>
-      <c r="B7" s="31" t="s">
-        <v>72</v>
+      <c r="B7" s="81" t="s">
+        <v>175</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>142</v>
+      <c r="C7" s="82" t="s">
+        <v>182</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>51</v>
+      <c r="D7" s="83" t="s">
+        <v>44</v>
       </c>
-      <c r="E7" s="34" t="s">
-        <v>3</v>
+      <c r="E7" s="82" t="s">
+        <v>190</v>
       </c>
-      <c r="F7" s="35">
-        <v>36526</v>
+      <c r="F7" s="84">
+        <v>23548</v>
       </c>
       <c r="G7" s="36">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="H7" s="48" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I7" s="67" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L7" s="39">
         <v>1</v>
@@ -49117,14 +49154,14 @@
         <v>1</v>
       </c>
       <c r="N7" s="40" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="O7" s="41">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="P7" s="40" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="41">
         <f t="shared" si="2"/>
@@ -49137,16 +49174,16 @@
         <v>109.5595</v>
       </c>
       <c r="T7" s="43" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="U7" s="43" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="V7" s="43" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="W7" s="43" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="X7" s="44">
         <v>3</v>
@@ -49163,61 +49200,61 @@
       <c r="AC7" s="44"/>
       <c r="AD7" s="69"/>
       <c r="AE7" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF7" s="70">
         <v>1600006544221</v>
       </c>
       <c r="AG7" s="69" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="AH7" s="45"/>
       <c r="AI7" s="46" t="str">
         <f t="shared" si="4"/>
-        <v>0000031600006544221Nama PB 3</v>
+        <v>960504521600006544221APOLONIA KORAIN</v>
       </c>
       <c r="AK7" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL7" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>26 Tahun</v>
+        <v>62 Tahun</v>
       </c>
     </row>
-    <row r="8" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="47">
         <v>4</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>79</v>
+      <c r="B8" s="81" t="s">
+        <v>176</v>
       </c>
-      <c r="C8" s="32" t="s">
-        <v>143</v>
+      <c r="C8" s="82" t="s">
+        <v>183</v>
       </c>
-      <c r="D8" s="33" t="s">
-        <v>51</v>
+      <c r="D8" s="83" t="s">
+        <v>45</v>
       </c>
-      <c r="E8" s="34" t="s">
-        <v>3</v>
+      <c r="E8" s="82" t="s">
+        <v>190</v>
       </c>
-      <c r="F8" s="35">
-        <v>36526</v>
+      <c r="F8" s="84">
+        <v>35903</v>
       </c>
       <c r="G8" s="36">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H8" s="48" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I8" s="67" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L8" s="39">
         <v>1</v>
@@ -49226,14 +49263,14 @@
         <v>1</v>
       </c>
       <c r="N8" s="40" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="O8" s="41">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="P8" s="40" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="41">
         <f t="shared" si="2"/>
@@ -49246,16 +49283,16 @@
         <v>109.5635</v>
       </c>
       <c r="T8" s="43" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="U8" s="43" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="V8" s="43" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="W8" s="43" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="X8" s="44">
         <v>4</v>
@@ -49272,61 +49309,61 @@
       <c r="AC8" s="44"/>
       <c r="AD8" s="69"/>
       <c r="AE8" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF8" s="70">
         <v>1600006544239</v>
       </c>
       <c r="AG8" s="69" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="AH8" s="45"/>
       <c r="AI8" s="46" t="str">
         <f t="shared" si="4"/>
-        <v>0000041600006544239Nama PB 4</v>
+        <v>960504531600006544239BARTOLOMEUS KORAIN</v>
       </c>
       <c r="AK8" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL8" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>26 Tahun</v>
+        <v>28 Tahun</v>
       </c>
     </row>
-    <row r="9" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="47">
         <v>5</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>86</v>
+      <c r="B9" s="81" t="s">
+        <v>177</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>144</v>
+      <c r="C9" s="82" t="s">
+        <v>184</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>51</v>
+      <c r="D9" s="83" t="s">
+        <v>44</v>
       </c>
-      <c r="E9" s="34" t="s">
-        <v>3</v>
+      <c r="E9" s="82" t="s">
+        <v>190</v>
       </c>
-      <c r="F9" s="35">
-        <v>36526</v>
+      <c r="F9" s="84">
+        <v>30349</v>
       </c>
       <c r="G9" s="36">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H9" s="48" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I9" s="67" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L9" s="39">
         <v>1</v>
@@ -49335,14 +49372,14 @@
         <v>1</v>
       </c>
       <c r="N9" s="40" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="O9" s="41">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="P9" s="40" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="Q9" s="41">
         <f t="shared" si="2"/>
@@ -49355,16 +49392,16 @@
         <v>109.5676</v>
       </c>
       <c r="T9" s="43" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="U9" s="43" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="V9" s="43" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="W9" s="43" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="X9" s="44">
         <v>5</v>
@@ -49381,61 +49418,61 @@
       <c r="AC9" s="44"/>
       <c r="AD9" s="69"/>
       <c r="AE9" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF9" s="70">
         <v>1600006544247</v>
       </c>
       <c r="AG9" s="69" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="AH9" s="45"/>
       <c r="AI9" s="46" t="str">
         <f t="shared" si="4"/>
-        <v>0000051600006544247Nama PB 5</v>
+        <v>960504571600006544247MATILDA TAA</v>
       </c>
       <c r="AK9" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL9" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>26 Tahun</v>
+        <v>43 Tahun</v>
       </c>
     </row>
-    <row r="10" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="47">
         <v>6</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>93</v>
+      <c r="B10" s="81" t="s">
+        <v>178</v>
       </c>
-      <c r="C10" s="32" t="s">
-        <v>145</v>
+      <c r="C10" s="82" t="s">
+        <v>185</v>
       </c>
-      <c r="D10" s="33" t="s">
-        <v>51</v>
+      <c r="D10" s="83" t="s">
+        <v>188</v>
       </c>
-      <c r="E10" s="34" t="s">
-        <v>3</v>
+      <c r="E10" s="82" t="s">
+        <v>191</v>
       </c>
-      <c r="F10" s="35">
-        <v>36526</v>
+      <c r="F10" s="84">
+        <v>31124</v>
       </c>
       <c r="G10" s="36">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="H10" s="48" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I10" s="67" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L10" s="39">
         <v>1</v>
@@ -49444,14 +49481,14 @@
         <v>1</v>
       </c>
       <c r="N10" s="40" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="O10" s="41">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="P10" s="40" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="41">
         <f t="shared" si="2"/>
@@ -49464,16 +49501,16 @@
         <v>109.5591</v>
       </c>
       <c r="T10" s="43" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="U10" s="43" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="V10" s="43" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="W10" s="43" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="X10" s="44">
         <v>6</v>
@@ -49490,61 +49527,61 @@
       <c r="AC10" s="44"/>
       <c r="AD10" s="69"/>
       <c r="AE10" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF10" s="70">
         <v>1600006545038</v>
       </c>
       <c r="AG10" s="69" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="AH10" s="45"/>
       <c r="AI10" s="46" t="str">
         <f t="shared" si="4"/>
-        <v>0000061600006545038Nama PB 6</v>
+        <v>960504581600006545038MONICA KORAIN</v>
       </c>
       <c r="AK10" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL10" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>26 Tahun</v>
+        <v>41 Tahun</v>
       </c>
     </row>
-    <row r="11" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="47">
         <v>7</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>99</v>
+      <c r="B11" s="81" t="s">
+        <v>179</v>
       </c>
-      <c r="C11" s="32" t="s">
-        <v>146</v>
+      <c r="C11" s="82" t="s">
+        <v>186</v>
       </c>
-      <c r="D11" s="33" t="s">
-        <v>51</v>
+      <c r="D11" s="83" t="s">
+        <v>45</v>
       </c>
-      <c r="E11" s="34" t="s">
-        <v>3</v>
+      <c r="E11" s="82" t="s">
+        <v>190</v>
       </c>
-      <c r="F11" s="35">
-        <v>36526</v>
+      <c r="F11" s="84">
+        <v>30727</v>
       </c>
       <c r="G11" s="36">
         <f t="shared" ca="1" si="1"/>
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H11" s="48" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I11" s="67" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L11" s="39">
         <v>1</v>
@@ -49553,14 +49590,14 @@
         <v>1</v>
       </c>
       <c r="N11" s="40" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="O11" s="41">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="P11" s="40" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="Q11" s="41">
         <f t="shared" si="2"/>
@@ -49573,16 +49610,16 @@
         <v>109.5592</v>
       </c>
       <c r="T11" s="43" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="U11" s="43" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="V11" s="43" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="W11" s="43" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="X11" s="44">
         <v>7</v>
@@ -49599,46 +49636,52 @@
       <c r="AC11" s="44"/>
       <c r="AD11" s="69"/>
       <c r="AE11" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF11" s="70">
         <v>1600006545020</v>
       </c>
       <c r="AG11" s="69" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="AH11" s="45"/>
       <c r="AI11" s="46" t="str">
         <f t="shared" si="4"/>
-        <v>0000071600006545020Nama PB 7</v>
+        <v>960504601600006545020PASKALIS YUMTE</v>
       </c>
       <c r="AK11" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL11" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>26 Tahun</v>
+        <v>42 Tahun</v>
       </c>
     </row>
-    <row r="12" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="47">
         <v>8</v>
       </c>
-      <c r="B12" s="31" t="s">
-        <v>160</v>
+      <c r="B12" s="81" t="s">
+        <v>180</v>
       </c>
-      <c r="C12" s="32" t="s">
-        <v>147</v>
+      <c r="C12" s="82" t="s">
+        <v>187</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="35"/>
+      <c r="D12" s="83" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="82" t="s">
+        <v>192</v>
+      </c>
+      <c r="F12" s="84">
+        <v>29137</v>
+      </c>
       <c r="G12" s="36"/>
       <c r="H12" s="48"/>
       <c r="I12" s="67"/>
       <c r="J12" s="4"/>
       <c r="K12" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L12" s="39">
         <v>2</v>
@@ -49664,36 +49707,36 @@
       <c r="AC12" s="44"/>
       <c r="AD12" s="69"/>
       <c r="AE12" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF12" s="70">
         <v>1600006544254</v>
       </c>
       <c r="AG12" s="69" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AH12" s="45"/>
       <c r="AI12" s="46" t="str">
         <f t="shared" si="4"/>
-        <v>0000081600006544254Nama PB 8</v>
+        <v>960504641600006544254WIHELMUS KORAIN</v>
       </c>
       <c r="AK12" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL12" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="13" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="47">
         <v>9</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="D13" s="33"/>
       <c r="E13" s="34"/>
@@ -49703,7 +49746,7 @@
       <c r="I13" s="67"/>
       <c r="J13" s="4"/>
       <c r="K13" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L13" s="39">
         <v>2</v>
@@ -49729,13 +49772,13 @@
       <c r="AC13" s="44"/>
       <c r="AD13" s="69"/>
       <c r="AE13" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF13" s="70">
         <v>1600006544262</v>
       </c>
       <c r="AG13" s="69" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AH13" s="45"/>
       <c r="AI13" s="46" t="str">
@@ -49743,22 +49786,22 @@
         <v>0000091600006544262Nama PB 9</v>
       </c>
       <c r="AK13" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL13" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="14" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="47">
         <v>10</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="34"/>
@@ -49768,7 +49811,7 @@
       <c r="I14" s="67"/>
       <c r="J14" s="4"/>
       <c r="K14" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L14" s="39">
         <v>2</v>
@@ -49794,13 +49837,13 @@
       <c r="AC14" s="44"/>
       <c r="AD14" s="69"/>
       <c r="AE14" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF14" s="70">
         <v>1600006544270</v>
       </c>
       <c r="AG14" s="69" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AH14" s="45"/>
       <c r="AI14" s="46" t="str">
@@ -49808,22 +49851,22 @@
         <v>0000101600006544270Nama PB 10</v>
       </c>
       <c r="AK14" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL14" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="15" spans="1:38" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="9"/>
@@ -49833,7 +49876,7 @@
       <c r="I15" s="66"/>
       <c r="J15" s="13"/>
       <c r="K15" s="14" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L15" s="15">
         <v>2</v>
@@ -49859,13 +49902,13 @@
       <c r="AC15" s="20"/>
       <c r="AD15" s="68"/>
       <c r="AE15" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF15" s="71">
         <v>1600006544288</v>
       </c>
       <c r="AG15" s="69" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AH15" s="21"/>
       <c r="AI15" s="22" t="str">
@@ -49873,22 +49916,22 @@
         <v>0000111600006544288Nama PB 11</v>
       </c>
       <c r="AK15" s="23" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL15" s="23" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="16" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="47">
         <v>12</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="34"/>
@@ -49898,7 +49941,7 @@
       <c r="I16" s="67"/>
       <c r="J16" s="4"/>
       <c r="K16" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L16" s="39">
         <v>2</v>
@@ -49924,13 +49967,13 @@
       <c r="AC16" s="44"/>
       <c r="AD16" s="69"/>
       <c r="AE16" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF16" s="70">
         <v>1600006544296</v>
       </c>
       <c r="AG16" s="69" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AH16" s="45"/>
       <c r="AI16" s="46" t="str">
@@ -49938,22 +49981,22 @@
         <v>0000121600006544296Nama PB 12</v>
       </c>
       <c r="AK16" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL16" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="17" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="47">
         <v>13</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="34"/>
@@ -49963,7 +50006,7 @@
       <c r="I17" s="67"/>
       <c r="J17" s="4"/>
       <c r="K17" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L17" s="39">
         <v>2</v>
@@ -49989,13 +50032,13 @@
       <c r="AC17" s="44"/>
       <c r="AD17" s="69"/>
       <c r="AE17" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF17" s="70">
         <v>1600006544304</v>
       </c>
       <c r="AG17" s="69" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AH17" s="45"/>
       <c r="AI17" s="46" t="str">
@@ -50003,22 +50046,22 @@
         <v>0000131600006544304Nama PB 13</v>
       </c>
       <c r="AK17" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL17" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="18" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="47">
         <v>14</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="34"/>
@@ -50028,7 +50071,7 @@
       <c r="I18" s="67"/>
       <c r="J18" s="4"/>
       <c r="K18" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L18" s="39">
         <v>2</v>
@@ -50054,13 +50097,13 @@
       <c r="AC18" s="44"/>
       <c r="AD18" s="69"/>
       <c r="AE18" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF18" s="70">
         <v>1600006544312</v>
       </c>
       <c r="AG18" s="69" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AH18" s="45"/>
       <c r="AI18" s="46" t="str">
@@ -50068,22 +50111,22 @@
         <v>0000141600006544312Nama PB 14</v>
       </c>
       <c r="AK18" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL18" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="19" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="47">
         <v>15</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="34"/>
@@ -50093,7 +50136,7 @@
       <c r="I19" s="67"/>
       <c r="J19" s="4"/>
       <c r="K19" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L19" s="39">
         <v>2</v>
@@ -50119,13 +50162,13 @@
       <c r="AC19" s="44"/>
       <c r="AD19" s="69"/>
       <c r="AE19" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF19" s="70">
         <v>1600006551267</v>
       </c>
       <c r="AG19" s="69" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AH19" s="45"/>
       <c r="AI19" s="46" t="str">
@@ -50133,22 +50176,22 @@
         <v>0000151600006551267Nama PB 15</v>
       </c>
       <c r="AK19" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL19" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="20" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="47">
         <v>16</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D20" s="33"/>
       <c r="E20" s="34"/>
@@ -50158,7 +50201,7 @@
       <c r="I20" s="67"/>
       <c r="J20" s="4"/>
       <c r="K20" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L20" s="39">
         <v>2</v>
@@ -50184,13 +50227,13 @@
       <c r="AC20" s="44"/>
       <c r="AD20" s="69"/>
       <c r="AE20" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF20" s="70">
         <v>1600006544320</v>
       </c>
       <c r="AG20" s="69" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AH20" s="45"/>
       <c r="AI20" s="46" t="str">
@@ -50198,22 +50241,22 @@
         <v>0000161600006544320Nama PB 16</v>
       </c>
       <c r="AK20" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL20" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="21" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="47">
         <v>17</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D21" s="33"/>
       <c r="E21" s="34"/>
@@ -50223,7 +50266,7 @@
       <c r="I21" s="67"/>
       <c r="J21" s="4"/>
       <c r="K21" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L21" s="39">
         <v>1</v>
@@ -50249,13 +50292,13 @@
       <c r="AC21" s="44"/>
       <c r="AD21" s="69"/>
       <c r="AE21" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF21" s="70">
         <v>1600006544346</v>
       </c>
       <c r="AG21" s="69" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="AH21" s="45"/>
       <c r="AI21" s="46" t="str">
@@ -50263,22 +50306,22 @@
         <v>0000171600006544346Nama PB 17</v>
       </c>
       <c r="AK21" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL21" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="22" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="47">
         <v>18</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="34"/>
@@ -50288,7 +50331,7 @@
       <c r="I22" s="67"/>
       <c r="J22" s="4"/>
       <c r="K22" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L22" s="39">
         <v>1</v>
@@ -50314,13 +50357,13 @@
       <c r="AC22" s="44"/>
       <c r="AD22" s="69"/>
       <c r="AE22" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF22" s="70">
         <v>1600006544353</v>
       </c>
       <c r="AG22" s="69" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="AH22" s="45"/>
       <c r="AI22" s="46" t="str">
@@ -50328,22 +50371,22 @@
         <v>0000181600006544353Nama PB 18</v>
       </c>
       <c r="AK22" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL22" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="23" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="47">
         <v>19</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="34"/>
@@ -50353,7 +50396,7 @@
       <c r="I23" s="67"/>
       <c r="J23" s="4"/>
       <c r="K23" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L23" s="39">
         <v>1</v>
@@ -50379,13 +50422,13 @@
       <c r="AC23" s="44"/>
       <c r="AD23" s="69"/>
       <c r="AE23" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF23" s="70">
         <v>1600006586008</v>
       </c>
       <c r="AG23" s="69" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="AH23" s="45"/>
       <c r="AI23" s="46" t="str">
@@ -50393,22 +50436,22 @@
         <v>0000191600006586008Nama PB 19</v>
       </c>
       <c r="AK23" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL23" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="24" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="47">
         <v>20</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="34"/>
@@ -50418,7 +50461,7 @@
       <c r="I24" s="67"/>
       <c r="J24" s="4"/>
       <c r="K24" s="38" t="s">
-        <v>173</v>
+        <v>151</v>
       </c>
       <c r="L24" s="39">
         <v>1</v>
@@ -50444,13 +50487,13 @@
       <c r="AC24" s="44"/>
       <c r="AD24" s="69"/>
       <c r="AE24" s="69" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="AF24" s="70">
         <v>1600006544361</v>
       </c>
       <c r="AG24" s="69" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="AH24" s="45"/>
       <c r="AI24" s="46" t="str">
@@ -50458,48 +50501,48 @@
         <v>0000201600006544361Nama PB 20</v>
       </c>
       <c r="AK24" s="25" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="AL24" s="25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Tahun</v>
       </c>
     </row>
-    <row r="25" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="I26" s="50" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="J26" s="49" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="N26" s="50" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="O26" s="51"/>
       <c r="P26" s="50" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="R26" s="49" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="AF26" s="50" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
-    <row r="27" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="52" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C27" s="53" t="s">
-        <v>174</v>
+        <v>152</v>
       </c>
-      <c r="D27" s="79" t="s">
-        <v>109</v>
+      <c r="D27" s="80" t="s">
+        <v>96</v>
       </c>
-      <c r="E27" s="79"/>
+      <c r="E27" s="80"/>
       <c r="J27" s="49" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="R27" s="42">
         <v>-7.4668999999999999</v>
@@ -50508,74 +50551,54 @@
         <v>109.5536</v>
       </c>
     </row>
-    <row r="28" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="52" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C28" s="54" t="str">
         <f>VLOOKUP(D28,$A$2:$C$24,3,FALSE)</f>
-        <v>Nama PB 1</v>
+        <v xml:space="preserve">AGNES ASSEM </v>
       </c>
       <c r="D28" s="78">
         <v>1</v>
       </c>
       <c r="E28" s="78"/>
     </row>
-    <row r="29" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="52" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C29" s="54" t="str">
         <f>VLOOKUP(D29,$A$2:$C$24,3,FALSE)</f>
-        <v>Nama PB 4</v>
+        <v>BARTOLOMEUS KORAIN</v>
       </c>
       <c r="D29" s="78">
         <v>4</v>
       </c>
       <c r="E29" s="78"/>
     </row>
-    <row r="30" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="52" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C30" s="54" t="str">
         <f>VLOOKUP(D30,$A$2:$C$24,3,FALSE)</f>
-        <v>Nama PB 6</v>
+        <v>MONICA KORAIN</v>
       </c>
       <c r="D30" s="78">
         <v>6</v>
       </c>
       <c r="E30" s="78"/>
     </row>
-    <row r="31" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="10:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="10:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J33" s="55"/>
     </row>
-    <row r="34" spans="10:10" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" spans="10:10" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" spans="10:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" spans="10:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="AE2:AE4"/>
-    <mergeCell ref="AF2:AF4"/>
-    <mergeCell ref="AA2:AA4"/>
-    <mergeCell ref="AB2:AB4"/>
-    <mergeCell ref="AC2:AC4"/>
-    <mergeCell ref="AD2:AD4"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="O2:O4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
     <mergeCell ref="AG2:AG4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
@@ -50592,47 +50615,67 @@
     <mergeCell ref="R2:S4"/>
     <mergeCell ref="T2:W2"/>
     <mergeCell ref="J2:J4"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="AE2:AE4"/>
+    <mergeCell ref="AF2:AF4"/>
+    <mergeCell ref="AA2:AA4"/>
+    <mergeCell ref="AB2:AB4"/>
+    <mergeCell ref="AC2:AC4"/>
+    <mergeCell ref="AD2:AD4"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="C5:C24">
-    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:N24">
-    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N15:N24">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22:N24">
-    <cfRule type="duplicateValues" dxfId="17" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P24">
-    <cfRule type="duplicateValues" dxfId="15" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P15:P24">
-    <cfRule type="duplicateValues" dxfId="9" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P22:P24">
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="NO KK" sqref="P5:P24" xr:uid="{2FF7C5AD-0759-3641-A164-C0AE401DB8AD}">

--- a/format-laporan/hari-minggu-2026/Format Baru Permen 6 2026 (1) (1)/Fix/00 Database.xlsx
+++ b/format-laporan/hari-minggu-2026/Format Baru Permen 6 2026 (1) (1)/Fix/00 Database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSPS-2026\format-laporan\hari-minggu-2026\Format Baru Permen 6 2026 (1) (1)\Fix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D132E7-43B5-4C61-8827-008C0A10B17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83840B4-1E00-44C8-905D-31E50C5C08C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{F26A00DE-12D0-554C-ABD8-D44599DA1687}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{F26A00DE-12D0-554C-ABD8-D44599DA1687}"/>
   </bookViews>
   <sheets>
     <sheet name="Base_01" sheetId="1" r:id="rId1"/>
@@ -141,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="192">
   <si>
     <t>Distrik</t>
   </si>
@@ -287,16 +287,7 @@
     <t>Penamaan Folder</t>
   </si>
   <si>
-    <t>Mengurus Rumah Tangga</t>
-  </si>
-  <si>
     <t>1.800.000</t>
-  </si>
-  <si>
-    <t>3310080902970001</t>
-  </si>
-  <si>
-    <t>…………….</t>
   </si>
   <si>
     <t>Utara 1</t>
@@ -314,13 +305,7 @@
     <t xml:space="preserve"> Tahun</t>
   </si>
   <si>
-    <t>Petani</t>
-  </si>
-  <si>
     <t>2.000.000</t>
-  </si>
-  <si>
-    <t>3304160101810004</t>
   </si>
   <si>
     <t>Utara 2</t>
@@ -335,12 +320,6 @@
     <t>Barat 2</t>
   </si>
   <si>
-    <t>Buruh</t>
-  </si>
-  <si>
-    <t>3304160101820004</t>
-  </si>
-  <si>
     <t>Utara 3</t>
   </si>
   <si>
@@ -351,12 +330,6 @@
   </si>
   <si>
     <t>Barat 3</t>
-  </si>
-  <si>
-    <t>Wiraswasta</t>
-  </si>
-  <si>
-    <t>3304160101830004</t>
   </si>
   <si>
     <t>Utara 4</t>
@@ -371,12 +344,6 @@
     <t>Barat 4</t>
   </si>
   <si>
-    <t>Buruh Harian Lepas</t>
-  </si>
-  <si>
-    <t>3304160101840004</t>
-  </si>
-  <si>
     <t>Utara 5</t>
   </si>
   <si>
@@ -389,9 +356,6 @@
     <t>Barat 5</t>
   </si>
   <si>
-    <t>3304160101850004</t>
-  </si>
-  <si>
     <t>Utara 6</t>
   </si>
   <si>
@@ -402,9 +366,6 @@
   </si>
   <si>
     <t>Barat 6</t>
-  </si>
-  <si>
-    <t>3304160101860004</t>
   </si>
   <si>
     <t>Utara 7</t>
@@ -599,9 +560,6 @@
     <t>Jalan Kanal Victory</t>
   </si>
   <si>
-    <t>Membangun Bersama</t>
-  </si>
-  <si>
     <t>Tanggal Sosialisasi</t>
   </si>
   <si>
@@ -722,6 +680,45 @@
   <si>
     <t>SABES</t>
   </si>
+  <si>
+    <t xml:space="preserve">PEKERJAAN </t>
+  </si>
+  <si>
+    <t>PETANI</t>
+  </si>
+  <si>
+    <t>BELUM BEKERJA</t>
+  </si>
+  <si>
+    <t>9204055104640001</t>
+  </si>
+  <si>
+    <t>9204054107570003</t>
+  </si>
+  <si>
+    <t>9210016006640001</t>
+  </si>
+  <si>
+    <t>9109161804980001</t>
+  </si>
+  <si>
+    <t>9204054306840001</t>
+  </si>
+  <si>
+    <t>9204054102880002</t>
+  </si>
+  <si>
+    <t>9204050609860001</t>
+  </si>
+  <si>
+    <t>9204050910790001</t>
+  </si>
+  <si>
+    <t>WAYANE</t>
+  </si>
+  <si>
+    <t>SaCode</t>
+  </si>
 </sst>
 </file>
 
@@ -734,7 +731,7 @@
     <numFmt numFmtId="167" formatCode="[$-13809]d\ mmm\ yyyy;@"/>
     <numFmt numFmtId="168" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -878,8 +875,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -901,6 +911,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="11"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -971,7 +987,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
@@ -1082,10 +1098,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -1195,15 +1207,24 @@
     <xf numFmtId="1" fontId="6" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="4" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1217,20 +1238,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{E09FD1F8-35A6-454A-B7B2-8D124FC4FCA3}"/>
@@ -1238,16 +1251,6 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7589842B-B365-B946-A563-BCB40ACE3300}"/>
   </cellStyles>
   <dxfs count="26">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1480,6 +1483,16 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -48418,217 +48431,217 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B2" s="56" t="s">
-        <v>162</v>
+      <c r="B2" s="55" t="s">
+        <v>148</v>
       </c>
-      <c r="C2" s="57" t="s">
-        <v>163</v>
+      <c r="C2" s="56" t="s">
+        <v>149</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="57" t="s">
-        <v>164</v>
+      <c r="C3" s="56" t="s">
+        <v>150</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="56" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="64" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="58">
         <v>98277</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="57" t="s">
-        <v>165</v>
+      <c r="C7" s="56" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="60">
+      <c r="C8" s="59">
         <v>40000000</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B9" s="58" t="str">
+      <c r="B9" s="57" t="str">
         <f>"Nama Kepala "&amp;B2</f>
         <v>Nama Kepala Kampung</v>
       </c>
-      <c r="C9" s="57" t="s">
-        <v>166</v>
+      <c r="C9" s="56" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B10" s="58" t="str">
+      <c r="B10" s="57" t="str">
         <f>"NIP "&amp;F24</f>
         <v xml:space="preserve">NIP </v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="56" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="57" t="s">
-        <v>167</v>
+      <c r="C11" s="56" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="61">
+      <c r="C12" s="60">
         <v>3766000</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="61">
+      <c r="C13" s="60">
         <v>3766000</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="42" x14ac:dyDescent="0.35">
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="62" t="s">
+      <c r="C14" s="61" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="62" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="62" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="58" t="str">
+      <c r="B17" s="57" t="str">
         <f>"Koordinator "&amp;B4</f>
         <v>Koordinator Kota</v>
       </c>
-      <c r="C17" s="63" t="s">
-        <v>168</v>
+      <c r="C17" s="62" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="56" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="57" t="s">
-        <v>169</v>
+      <c r="C19" s="56" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="64"/>
+      <c r="B20" s="63"/>
       <c r="C20" s="24"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B26" s="58" t="s">
-        <v>103</v>
+      <c r="B26" s="57" t="s">
+        <v>90</v>
       </c>
-      <c r="C26" s="57" t="s">
-        <v>170</v>
+      <c r="C26" s="56" t="s">
+        <v>156</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B27" s="58" t="s">
-        <v>124</v>
+      <c r="B27" s="57" t="s">
+        <v>111</v>
       </c>
-      <c r="C27" s="57" t="s">
-        <v>170</v>
+      <c r="C27" s="56" t="s">
+        <v>156</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B28" s="58" t="s">
-        <v>126</v>
+      <c r="B28" s="57" t="s">
+        <v>113</v>
       </c>
-      <c r="C28" s="57" t="s">
-        <v>123</v>
+      <c r="C28" s="56" t="s">
+        <v>110</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B29" s="58" t="s">
-        <v>153</v>
+      <c r="B29" s="57" t="s">
+        <v>139</v>
       </c>
-      <c r="C29" s="57" t="s">
-        <v>171</v>
+      <c r="C29" s="56" t="s">
+        <v>157</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -48703,13 +48716,13 @@
       <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:38" s="27" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="78" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="79" t="s">
@@ -48724,144 +48737,144 @@
       <c r="G2" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="73" t="s">
+      <c r="H2" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="73" t="s">
-        <v>108</v>
+      <c r="I2" s="78" t="s">
+        <v>95</v>
       </c>
-      <c r="J2" s="73" t="s">
+      <c r="J2" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="73" t="s">
+      <c r="K2" s="78" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73" t="s">
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="75" t="s">
+      <c r="O2" s="80" t="s">
         <v>31</v>
       </c>
-      <c r="P2" s="73" t="s">
+      <c r="P2" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="75" t="s">
+      <c r="Q2" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="R2" s="73" t="s">
+      <c r="R2" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="73"/>
-      <c r="T2" s="73" t="s">
+      <c r="S2" s="78"/>
+      <c r="T2" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="U2" s="73"/>
-      <c r="V2" s="73"/>
-      <c r="W2" s="73"/>
-      <c r="X2" s="73" t="s">
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
+      <c r="W2" s="78"/>
+      <c r="X2" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="Y2" s="73"/>
-      <c r="Z2" s="73"/>
-      <c r="AA2" s="75" t="s">
-        <v>116</v>
+      <c r="Y2" s="78"/>
+      <c r="Z2" s="78"/>
+      <c r="AA2" s="80" t="s">
+        <v>103</v>
       </c>
-      <c r="AB2" s="75" t="s">
-        <v>154</v>
+      <c r="AB2" s="80" t="s">
+        <v>140</v>
       </c>
-      <c r="AC2" s="75" t="s">
-        <v>117</v>
+      <c r="AC2" s="80" t="s">
+        <v>104</v>
       </c>
-      <c r="AD2" s="75" t="s">
-        <v>118</v>
+      <c r="AD2" s="80" t="s">
+        <v>105</v>
       </c>
-      <c r="AE2" s="73" t="s">
-        <v>155</v>
+      <c r="AE2" s="78" t="s">
+        <v>141</v>
       </c>
-      <c r="AF2" s="74" t="s">
-        <v>156</v>
+      <c r="AF2" s="85" t="s">
+        <v>142</v>
       </c>
-      <c r="AG2" s="73" t="s">
-        <v>158</v>
+      <c r="AG2" s="78" t="s">
+        <v>144</v>
       </c>
       <c r="AH2" s="29"/>
     </row>
     <row r="3" spans="1:38" s="27" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="73"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
       <c r="D3" s="79"/>
       <c r="E3" s="79"/>
       <c r="F3" s="79"/>
       <c r="G3" s="79"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73" t="s">
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="73" t="s">
+      <c r="L3" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="73" t="s">
+      <c r="M3" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="73"/>
-      <c r="O3" s="76"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="U3" s="73" t="s">
+      <c r="U3" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="V3" s="73" t="s">
+      <c r="V3" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="W3" s="73" t="s">
+      <c r="W3" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="X3" s="73"/>
-      <c r="Y3" s="73"/>
-      <c r="Z3" s="73"/>
-      <c r="AA3" s="76"/>
-      <c r="AB3" s="76"/>
-      <c r="AC3" s="76"/>
-      <c r="AD3" s="76"/>
-      <c r="AE3" s="73"/>
-      <c r="AF3" s="74"/>
-      <c r="AG3" s="73"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="78"/>
+      <c r="Z3" s="78"/>
+      <c r="AA3" s="81"/>
+      <c r="AB3" s="81"/>
+      <c r="AC3" s="81"/>
+      <c r="AD3" s="81"/>
+      <c r="AE3" s="78"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="78"/>
       <c r="AH3" s="29"/>
     </row>
     <row r="4" spans="1:38" s="27" customFormat="1" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="73"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
       <c r="D4" s="79"/>
       <c r="E4" s="79"/>
       <c r="F4" s="79"/>
       <c r="G4" s="79"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="W4" s="73"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="78"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="82"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+      <c r="U4" s="78"/>
+      <c r="V4" s="78"/>
+      <c r="W4" s="78"/>
       <c r="X4" s="28" t="s">
         <v>44</v>
       </c>
@@ -48871,13 +48884,13 @@
       <c r="Z4" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="AA4" s="77"/>
-      <c r="AB4" s="77"/>
-      <c r="AC4" s="77"/>
-      <c r="AD4" s="77"/>
-      <c r="AE4" s="73"/>
-      <c r="AF4" s="74"/>
-      <c r="AG4" s="73"/>
+      <c r="AA4" s="82"/>
+      <c r="AB4" s="82"/>
+      <c r="AC4" s="82"/>
+      <c r="AD4" s="82"/>
+      <c r="AE4" s="78"/>
+      <c r="AF4" s="85"/>
+      <c r="AG4" s="78"/>
       <c r="AH4" s="29"/>
       <c r="AI4" s="28" t="s">
         <v>47</v>
@@ -48888,113 +48901,113 @@
       <c r="A5" s="30">
         <v>1</v>
       </c>
-      <c r="B5" s="81" t="s">
-        <v>173</v>
+      <c r="B5" s="71" t="s">
+        <v>159</v>
       </c>
-      <c r="C5" s="82" t="s">
-        <v>172</v>
+      <c r="C5" s="72" t="s">
+        <v>158</v>
       </c>
-      <c r="D5" s="83" t="s">
+      <c r="D5" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="82" t="s">
-        <v>189</v>
+      <c r="E5" s="72" t="s">
+        <v>175</v>
       </c>
-      <c r="F5" s="84">
+      <c r="F5" s="74">
         <v>23478</v>
       </c>
       <c r="G5" s="36">
         <f ca="1">INT((TODAY()-F5)/365)</f>
         <v>62</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="I5" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="67" t="s">
-        <v>109</v>
+      <c r="K5" s="77" t="s">
+        <v>190</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>49</v>
+      <c r="L5" s="38">
+        <v>0</v>
       </c>
-      <c r="K5" s="38" t="s">
-        <v>151</v>
+      <c r="M5" s="38">
+        <v>0</v>
       </c>
-      <c r="L5" s="39">
-        <v>1</v>
+      <c r="N5" s="76" t="s">
+        <v>182</v>
       </c>
-      <c r="M5" s="39">
-        <v>1</v>
-      </c>
-      <c r="N5" s="72" t="s">
-        <v>50</v>
-      </c>
-      <c r="O5" s="41">
+      <c r="O5" s="40">
         <f>LEN(N5)</f>
         <v>16</v>
       </c>
-      <c r="P5" s="40" t="s">
+      <c r="P5" s="76" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q5" s="40">
+        <f>LEN(P5)</f>
+        <v>16</v>
+      </c>
+      <c r="R5" s="41">
+        <v>-7.4668999999999999</v>
+      </c>
+      <c r="S5" s="41">
+        <v>109.5536</v>
+      </c>
+      <c r="T5" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="U5" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="V5" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="Q5" s="41">
-        <f>LEN(P5)</f>
-        <v>6</v>
-      </c>
-      <c r="R5" s="42">
-        <v>-7.4668999999999999</v>
-      </c>
-      <c r="S5" s="42">
-        <v>109.5536</v>
-      </c>
-      <c r="T5" s="43" t="s">
+      <c r="W5" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="U5" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="V5" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="W5" s="43" t="s">
-        <v>55</v>
-      </c>
-      <c r="X5" s="44">
+      <c r="X5" s="43">
         <v>1</v>
       </c>
-      <c r="Y5" s="44">
+      <c r="Y5" s="43">
         <v>10</v>
       </c>
-      <c r="Z5" s="44">
+      <c r="Z5" s="43">
         <f>X5*Y5</f>
         <v>10</v>
       </c>
-      <c r="AA5" s="44" t="s">
-        <v>120</v>
+      <c r="AA5" s="43" t="s">
+        <v>107</v>
       </c>
-      <c r="AB5" s="69" t="s">
-        <v>122</v>
+      <c r="AB5" s="68" t="s">
+        <v>109</v>
       </c>
-      <c r="AC5" s="44" t="s">
-        <v>121</v>
+      <c r="AC5" s="43" t="s">
+        <v>108</v>
       </c>
-      <c r="AD5" s="69">
+      <c r="AD5" s="68">
         <v>2020</v>
       </c>
-      <c r="AE5" s="69" t="s">
-        <v>157</v>
+      <c r="AE5" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF5" s="70">
+      <c r="AF5" s="69">
         <v>1600006544205</v>
       </c>
-      <c r="AG5" s="69" t="s">
-        <v>159</v>
+      <c r="AG5" s="68" t="s">
+        <v>145</v>
       </c>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="46" t="str">
+      <c r="AH5" s="44"/>
+      <c r="AI5" s="45" t="str">
         <f>B5&amp;AF5&amp;C5</f>
         <v xml:space="preserve">960504501600006544205AGNES ASSEM </v>
       </c>
       <c r="AK5" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL5" s="25" t="str">
         <f t="shared" ref="AL5:AL24" ca="1" si="0">G5&amp;AK5</f>
@@ -49002,110 +49015,110 @@
       </c>
     </row>
     <row r="6" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="47">
+      <c r="A6" s="46">
         <v>2</v>
       </c>
-      <c r="B6" s="81" t="s">
-        <v>174</v>
+      <c r="B6" s="71" t="s">
+        <v>160</v>
       </c>
-      <c r="C6" s="82" t="s">
-        <v>181</v>
+      <c r="C6" s="72" t="s">
+        <v>167</v>
       </c>
-      <c r="D6" s="83" t="s">
+      <c r="D6" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="82" t="s">
-        <v>190</v>
+      <c r="E6" s="72" t="s">
+        <v>176</v>
       </c>
-      <c r="F6" s="84">
+      <c r="F6" s="74">
         <v>21002</v>
       </c>
       <c r="G6" s="36">
         <f t="shared" ref="G6:G11" ca="1" si="1">INT((TODAY()-F6)/365)</f>
         <v>69</v>
       </c>
-      <c r="H6" s="48" t="s">
-        <v>57</v>
+      <c r="H6" s="75" t="s">
+        <v>180</v>
       </c>
-      <c r="I6" s="67" t="s">
-        <v>110</v>
+      <c r="I6" s="66" t="s">
+        <v>97</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
-      <c r="K6" s="38" t="s">
-        <v>151</v>
+      <c r="K6" s="77" t="s">
+        <v>190</v>
       </c>
-      <c r="L6" s="39">
-        <v>1</v>
+      <c r="L6" s="38">
+        <v>0</v>
       </c>
-      <c r="M6" s="39">
-        <v>1</v>
+      <c r="M6" s="38">
+        <v>0</v>
       </c>
-      <c r="N6" s="40" t="s">
-        <v>59</v>
+      <c r="N6" s="76" t="s">
+        <v>183</v>
       </c>
-      <c r="O6" s="41">
+      <c r="O6" s="40">
         <f t="shared" ref="O6:Q11" si="2">LEN(N6)</f>
         <v>16</v>
       </c>
-      <c r="P6" s="40" t="s">
-        <v>51</v>
+      <c r="P6" s="76" t="s">
+        <v>183</v>
       </c>
-      <c r="Q6" s="41">
+      <c r="Q6" s="40">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>16</v>
       </c>
-      <c r="R6" s="42">
+      <c r="R6" s="41">
         <v>-7.4669999999999996</v>
       </c>
-      <c r="S6" s="42">
+      <c r="S6" s="41">
         <v>109.5594</v>
       </c>
-      <c r="T6" s="43" t="s">
-        <v>60</v>
+      <c r="T6" s="42" t="s">
+        <v>55</v>
       </c>
-      <c r="U6" s="43" t="s">
-        <v>61</v>
+      <c r="U6" s="42" t="s">
+        <v>56</v>
       </c>
-      <c r="V6" s="43" t="s">
-        <v>62</v>
+      <c r="V6" s="42" t="s">
+        <v>57</v>
       </c>
-      <c r="W6" s="43" t="s">
-        <v>63</v>
+      <c r="W6" s="42" t="s">
+        <v>58</v>
       </c>
-      <c r="X6" s="44">
+      <c r="X6" s="43">
         <v>2</v>
       </c>
-      <c r="Y6" s="44">
+      <c r="Y6" s="43">
         <v>10</v>
       </c>
-      <c r="Z6" s="44">
+      <c r="Z6" s="43">
         <f t="shared" ref="Z6:Z11" si="3">X6*Y6</f>
         <v>20</v>
       </c>
-      <c r="AA6" s="44" t="s">
-        <v>119</v>
+      <c r="AA6" s="43" t="s">
+        <v>106</v>
       </c>
-      <c r="AB6" s="69"/>
-      <c r="AC6" s="44"/>
-      <c r="AD6" s="69"/>
-      <c r="AE6" s="69" t="s">
-        <v>157</v>
+      <c r="AB6" s="68"/>
+      <c r="AC6" s="43"/>
+      <c r="AD6" s="68"/>
+      <c r="AE6" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF6" s="70">
+      <c r="AF6" s="69">
         <v>1600006544213</v>
       </c>
-      <c r="AG6" s="69" t="s">
-        <v>159</v>
+      <c r="AG6" s="68" t="s">
+        <v>145</v>
       </c>
-      <c r="AH6" s="45"/>
-      <c r="AI6" s="46" t="str">
+      <c r="AH6" s="44"/>
+      <c r="AI6" s="45" t="str">
         <f t="shared" ref="AI6:AI24" si="4">B6&amp;AF6&amp;C6</f>
         <v>960504511600006544213AKNES KORAIN</v>
       </c>
       <c r="AK6" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL6" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -49113,108 +49126,108 @@
       </c>
     </row>
     <row r="7" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="47">
+      <c r="A7" s="46">
         <v>3</v>
       </c>
-      <c r="B7" s="81" t="s">
-        <v>175</v>
+      <c r="B7" s="71" t="s">
+        <v>161</v>
       </c>
-      <c r="C7" s="82" t="s">
-        <v>182</v>
+      <c r="C7" s="72" t="s">
+        <v>168</v>
       </c>
-      <c r="D7" s="83" t="s">
+      <c r="D7" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="82" t="s">
-        <v>190</v>
+      <c r="E7" s="72" t="s">
+        <v>176</v>
       </c>
-      <c r="F7" s="84">
+      <c r="F7" s="74">
         <v>23548</v>
       </c>
       <c r="G7" s="36">
         <f t="shared" ca="1" si="1"/>
         <v>62</v>
       </c>
-      <c r="H7" s="48" t="s">
-        <v>64</v>
+      <c r="H7" s="75" t="s">
+        <v>180</v>
       </c>
-      <c r="I7" s="67" t="s">
-        <v>111</v>
+      <c r="I7" s="66" t="s">
+        <v>98</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
-      <c r="K7" s="38" t="s">
-        <v>151</v>
+      <c r="K7" s="77" t="s">
+        <v>190</v>
       </c>
-      <c r="L7" s="39">
-        <v>1</v>
+      <c r="L7" s="38">
+        <v>0</v>
       </c>
-      <c r="M7" s="39">
-        <v>1</v>
+      <c r="M7" s="38">
+        <v>0</v>
       </c>
-      <c r="N7" s="40" t="s">
-        <v>65</v>
+      <c r="N7" s="76" t="s">
+        <v>184</v>
       </c>
-      <c r="O7" s="41">
+      <c r="O7" s="40">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="P7" s="40" t="s">
-        <v>51</v>
+      <c r="P7" s="76" t="s">
+        <v>184</v>
       </c>
-      <c r="Q7" s="41">
+      <c r="Q7" s="40">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>16</v>
       </c>
-      <c r="R7" s="42">
+      <c r="R7" s="41">
         <v>-7.4688999999999997</v>
       </c>
-      <c r="S7" s="42">
+      <c r="S7" s="41">
         <v>109.5595</v>
       </c>
-      <c r="T7" s="43" t="s">
-        <v>66</v>
+      <c r="T7" s="42" t="s">
+        <v>59</v>
       </c>
-      <c r="U7" s="43" t="s">
-        <v>67</v>
+      <c r="U7" s="42" t="s">
+        <v>60</v>
       </c>
-      <c r="V7" s="43" t="s">
-        <v>68</v>
+      <c r="V7" s="42" t="s">
+        <v>61</v>
       </c>
-      <c r="W7" s="43" t="s">
-        <v>69</v>
+      <c r="W7" s="42" t="s">
+        <v>62</v>
       </c>
-      <c r="X7" s="44">
+      <c r="X7" s="43">
         <v>3</v>
       </c>
-      <c r="Y7" s="44">
+      <c r="Y7" s="43">
         <v>10</v>
       </c>
-      <c r="Z7" s="44">
+      <c r="Z7" s="43">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="AA7" s="44"/>
-      <c r="AB7" s="69"/>
-      <c r="AC7" s="44"/>
-      <c r="AD7" s="69"/>
-      <c r="AE7" s="69" t="s">
-        <v>157</v>
+      <c r="AA7" s="43"/>
+      <c r="AB7" s="68"/>
+      <c r="AC7" s="43"/>
+      <c r="AD7" s="68"/>
+      <c r="AE7" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF7" s="70">
+      <c r="AF7" s="69">
         <v>1600006544221</v>
       </c>
-      <c r="AG7" s="69" t="s">
-        <v>159</v>
+      <c r="AG7" s="68" t="s">
+        <v>145</v>
       </c>
-      <c r="AH7" s="45"/>
-      <c r="AI7" s="46" t="str">
+      <c r="AH7" s="44"/>
+      <c r="AI7" s="45" t="str">
         <f t="shared" si="4"/>
         <v>960504521600006544221APOLONIA KORAIN</v>
       </c>
       <c r="AK7" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL7" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -49222,108 +49235,108 @@
       </c>
     </row>
     <row r="8" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="47">
+      <c r="A8" s="46">
         <v>4</v>
       </c>
-      <c r="B8" s="81" t="s">
+      <c r="B8" s="71" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="72" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="73" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="72" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="82" t="s">
-        <v>183</v>
-      </c>
-      <c r="D8" s="83" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="82" t="s">
-        <v>190</v>
-      </c>
-      <c r="F8" s="84">
+      <c r="F8" s="74">
         <v>35903</v>
       </c>
       <c r="G8" s="36">
         <f t="shared" ca="1" si="1"/>
         <v>28</v>
       </c>
-      <c r="H8" s="48" t="s">
-        <v>70</v>
+      <c r="H8" s="75" t="s">
+        <v>181</v>
       </c>
-      <c r="I8" s="67" t="s">
-        <v>112</v>
+      <c r="I8" s="66" t="s">
+        <v>99</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
-      <c r="K8" s="38" t="s">
-        <v>151</v>
+      <c r="K8" s="77" t="s">
+        <v>190</v>
       </c>
-      <c r="L8" s="39">
-        <v>1</v>
+      <c r="L8" s="38">
+        <v>0</v>
       </c>
-      <c r="M8" s="39">
-        <v>1</v>
+      <c r="M8" s="38">
+        <v>0</v>
       </c>
-      <c r="N8" s="40" t="s">
-        <v>71</v>
+      <c r="N8" s="76" t="s">
+        <v>185</v>
       </c>
-      <c r="O8" s="41">
+      <c r="O8" s="40">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="P8" s="40" t="s">
-        <v>51</v>
+      <c r="P8" s="76" t="s">
+        <v>185</v>
       </c>
-      <c r="Q8" s="41">
+      <c r="Q8" s="40">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>16</v>
       </c>
-      <c r="R8" s="42">
+      <c r="R8" s="41">
         <v>-7.4710999999999999</v>
       </c>
-      <c r="S8" s="42">
+      <c r="S8" s="41">
         <v>109.5635</v>
       </c>
-      <c r="T8" s="43" t="s">
-        <v>72</v>
+      <c r="T8" s="42" t="s">
+        <v>63</v>
       </c>
-      <c r="U8" s="43" t="s">
-        <v>73</v>
+      <c r="U8" s="42" t="s">
+        <v>64</v>
       </c>
-      <c r="V8" s="43" t="s">
-        <v>74</v>
+      <c r="V8" s="42" t="s">
+        <v>65</v>
       </c>
-      <c r="W8" s="43" t="s">
-        <v>75</v>
+      <c r="W8" s="42" t="s">
+        <v>66</v>
       </c>
-      <c r="X8" s="44">
+      <c r="X8" s="43">
         <v>4</v>
       </c>
-      <c r="Y8" s="44">
+      <c r="Y8" s="43">
         <v>10</v>
       </c>
-      <c r="Z8" s="44">
+      <c r="Z8" s="43">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="AA8" s="44"/>
-      <c r="AB8" s="69"/>
-      <c r="AC8" s="44"/>
-      <c r="AD8" s="69"/>
-      <c r="AE8" s="69" t="s">
-        <v>157</v>
+      <c r="AA8" s="43"/>
+      <c r="AB8" s="68"/>
+      <c r="AC8" s="43"/>
+      <c r="AD8" s="68"/>
+      <c r="AE8" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF8" s="70">
+      <c r="AF8" s="69">
         <v>1600006544239</v>
       </c>
-      <c r="AG8" s="69" t="s">
-        <v>159</v>
+      <c r="AG8" s="68" t="s">
+        <v>145</v>
       </c>
-      <c r="AH8" s="45"/>
-      <c r="AI8" s="46" t="str">
+      <c r="AH8" s="44"/>
+      <c r="AI8" s="45" t="str">
         <f t="shared" si="4"/>
         <v>960504531600006544239BARTOLOMEUS KORAIN</v>
       </c>
       <c r="AK8" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL8" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -49331,108 +49344,108 @@
       </c>
     </row>
     <row r="9" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="47">
+      <c r="A9" s="46">
         <v>5</v>
       </c>
-      <c r="B9" s="81" t="s">
-        <v>177</v>
+      <c r="B9" s="71" t="s">
+        <v>163</v>
       </c>
-      <c r="C9" s="82" t="s">
-        <v>184</v>
+      <c r="C9" s="72" t="s">
+        <v>170</v>
       </c>
-      <c r="D9" s="83" t="s">
+      <c r="D9" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="82" t="s">
-        <v>190</v>
+      <c r="E9" s="72" t="s">
+        <v>176</v>
       </c>
-      <c r="F9" s="84">
+      <c r="F9" s="74">
         <v>30349</v>
       </c>
       <c r="G9" s="36">
         <f t="shared" ca="1" si="1"/>
         <v>43</v>
       </c>
-      <c r="H9" s="48" t="s">
-        <v>76</v>
+      <c r="H9" s="75" t="s">
+        <v>181</v>
       </c>
-      <c r="I9" s="67" t="s">
-        <v>113</v>
+      <c r="I9" s="66" t="s">
+        <v>100</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
-      <c r="K9" s="38" t="s">
-        <v>151</v>
+      <c r="K9" s="77" t="s">
+        <v>190</v>
       </c>
-      <c r="L9" s="39">
-        <v>1</v>
+      <c r="L9" s="38">
+        <v>0</v>
       </c>
-      <c r="M9" s="39">
-        <v>1</v>
+      <c r="M9" s="38">
+        <v>0</v>
       </c>
-      <c r="N9" s="40" t="s">
-        <v>77</v>
+      <c r="N9" s="76" t="s">
+        <v>186</v>
       </c>
-      <c r="O9" s="41">
+      <c r="O9" s="40">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="P9" s="40" t="s">
-        <v>51</v>
+      <c r="P9" s="76" t="s">
+        <v>186</v>
       </c>
-      <c r="Q9" s="41">
+      <c r="Q9" s="40">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>16</v>
       </c>
-      <c r="R9" s="42">
+      <c r="R9" s="41">
         <v>-7.4684999999999997</v>
       </c>
-      <c r="S9" s="42">
+      <c r="S9" s="41">
         <v>109.5676</v>
       </c>
-      <c r="T9" s="43" t="s">
-        <v>78</v>
+      <c r="T9" s="42" t="s">
+        <v>67</v>
       </c>
-      <c r="U9" s="43" t="s">
-        <v>79</v>
+      <c r="U9" s="42" t="s">
+        <v>68</v>
       </c>
-      <c r="V9" s="43" t="s">
-        <v>80</v>
+      <c r="V9" s="42" t="s">
+        <v>69</v>
       </c>
-      <c r="W9" s="43" t="s">
-        <v>81</v>
+      <c r="W9" s="42" t="s">
+        <v>70</v>
       </c>
-      <c r="X9" s="44">
+      <c r="X9" s="43">
         <v>5</v>
       </c>
-      <c r="Y9" s="44">
+      <c r="Y9" s="43">
         <v>10</v>
       </c>
-      <c r="Z9" s="44">
+      <c r="Z9" s="43">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="69"/>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="69"/>
-      <c r="AE9" s="69" t="s">
-        <v>157</v>
+      <c r="AA9" s="43"/>
+      <c r="AB9" s="68"/>
+      <c r="AC9" s="43"/>
+      <c r="AD9" s="68"/>
+      <c r="AE9" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF9" s="70">
+      <c r="AF9" s="69">
         <v>1600006544247</v>
       </c>
-      <c r="AG9" s="69" t="s">
-        <v>159</v>
+      <c r="AG9" s="68" t="s">
+        <v>145</v>
       </c>
-      <c r="AH9" s="45"/>
-      <c r="AI9" s="46" t="str">
+      <c r="AH9" s="44"/>
+      <c r="AI9" s="45" t="str">
         <f t="shared" si="4"/>
         <v>960504571600006544247MATILDA TAA</v>
       </c>
       <c r="AK9" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL9" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -49440,108 +49453,108 @@
       </c>
     </row>
     <row r="10" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="47">
+      <c r="A10" s="46">
         <v>6</v>
       </c>
-      <c r="B10" s="81" t="s">
-        <v>178</v>
+      <c r="B10" s="71" t="s">
+        <v>164</v>
       </c>
-      <c r="C10" s="82" t="s">
-        <v>185</v>
+      <c r="C10" s="72" t="s">
+        <v>171</v>
       </c>
-      <c r="D10" s="83" t="s">
-        <v>188</v>
+      <c r="D10" s="73" t="s">
+        <v>174</v>
       </c>
-      <c r="E10" s="82" t="s">
-        <v>191</v>
+      <c r="E10" s="72" t="s">
+        <v>177</v>
       </c>
-      <c r="F10" s="84">
+      <c r="F10" s="74">
         <v>31124</v>
       </c>
       <c r="G10" s="36">
         <f t="shared" ca="1" si="1"/>
         <v>41</v>
       </c>
-      <c r="H10" s="48" t="s">
-        <v>76</v>
+      <c r="H10" s="75" t="s">
+        <v>181</v>
       </c>
-      <c r="I10" s="67" t="s">
-        <v>114</v>
+      <c r="I10" s="66" t="s">
+        <v>101</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
-      <c r="K10" s="38" t="s">
-        <v>151</v>
+      <c r="K10" s="77" t="s">
+        <v>190</v>
       </c>
-      <c r="L10" s="39">
-        <v>1</v>
+      <c r="L10" s="38">
+        <v>0</v>
       </c>
-      <c r="M10" s="39">
-        <v>1</v>
+      <c r="M10" s="38">
+        <v>0</v>
       </c>
-      <c r="N10" s="40" t="s">
-        <v>82</v>
+      <c r="N10" s="76" t="s">
+        <v>187</v>
       </c>
-      <c r="O10" s="41">
+      <c r="O10" s="40">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="P10" s="40" t="s">
-        <v>51</v>
+      <c r="P10" s="76" t="s">
+        <v>187</v>
       </c>
-      <c r="Q10" s="41">
+      <c r="Q10" s="40">
         <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="R10" s="41">
+        <v>-7.4752999999999998</v>
+      </c>
+      <c r="S10" s="41">
+        <v>109.5591</v>
+      </c>
+      <c r="T10" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="U10" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="V10" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="W10" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="X10" s="43">
         <v>6</v>
       </c>
-      <c r="R10" s="42">
-        <v>-7.4752999999999998</v>
-      </c>
-      <c r="S10" s="42">
-        <v>109.5591</v>
-      </c>
-      <c r="T10" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="U10" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="V10" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="W10" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="X10" s="44">
-        <v>6</v>
-      </c>
-      <c r="Y10" s="44">
+      <c r="Y10" s="43">
         <v>10</v>
       </c>
-      <c r="Z10" s="44">
+      <c r="Z10" s="43">
         <f t="shared" si="3"/>
         <v>60</v>
       </c>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="69"/>
-      <c r="AC10" s="44"/>
-      <c r="AD10" s="69"/>
-      <c r="AE10" s="69" t="s">
-        <v>157</v>
+      <c r="AA10" s="43"/>
+      <c r="AB10" s="68"/>
+      <c r="AC10" s="43"/>
+      <c r="AD10" s="68"/>
+      <c r="AE10" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF10" s="70">
+      <c r="AF10" s="69">
         <v>1600006545038</v>
       </c>
-      <c r="AG10" s="69" t="s">
-        <v>159</v>
+      <c r="AG10" s="68" t="s">
+        <v>145</v>
       </c>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="46" t="str">
+      <c r="AH10" s="44"/>
+      <c r="AI10" s="45" t="str">
         <f t="shared" si="4"/>
         <v>960504581600006545038MONICA KORAIN</v>
       </c>
       <c r="AK10" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL10" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -49549,108 +49562,108 @@
       </c>
     </row>
     <row r="11" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="47">
+      <c r="A11" s="46">
         <v>7</v>
       </c>
-      <c r="B11" s="81" t="s">
-        <v>179</v>
+      <c r="B11" s="71" t="s">
+        <v>165</v>
       </c>
-      <c r="C11" s="82" t="s">
-        <v>186</v>
+      <c r="C11" s="72" t="s">
+        <v>172</v>
       </c>
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="82" t="s">
-        <v>190</v>
+      <c r="E11" s="72" t="s">
+        <v>176</v>
       </c>
-      <c r="F11" s="84">
+      <c r="F11" s="74">
         <v>30727</v>
       </c>
       <c r="G11" s="36">
         <f t="shared" ca="1" si="1"/>
         <v>42</v>
       </c>
-      <c r="H11" s="48" t="s">
-        <v>70</v>
+      <c r="H11" s="75" t="s">
+        <v>181</v>
       </c>
-      <c r="I11" s="67" t="s">
-        <v>115</v>
+      <c r="I11" s="66" t="s">
+        <v>102</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
-      <c r="K11" s="38" t="s">
-        <v>151</v>
+      <c r="K11" s="77" t="s">
+        <v>190</v>
       </c>
-      <c r="L11" s="39">
-        <v>1</v>
+      <c r="L11" s="38">
+        <v>0</v>
       </c>
-      <c r="M11" s="39">
-        <v>1</v>
+      <c r="M11" s="38">
+        <v>0</v>
       </c>
-      <c r="N11" s="40" t="s">
-        <v>87</v>
+      <c r="N11" s="76" t="s">
+        <v>188</v>
       </c>
-      <c r="O11" s="41">
+      <c r="O11" s="40">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="P11" s="40" t="s">
-        <v>51</v>
+      <c r="P11" s="76" t="s">
+        <v>188</v>
       </c>
-      <c r="Q11" s="41">
+      <c r="Q11" s="40">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>16</v>
       </c>
-      <c r="R11" s="42">
+      <c r="R11" s="41">
         <v>-7.4752999999999998</v>
       </c>
-      <c r="S11" s="42">
+      <c r="S11" s="41">
         <v>109.5592</v>
       </c>
-      <c r="T11" s="43" t="s">
-        <v>88</v>
+      <c r="T11" s="42" t="s">
+        <v>75</v>
       </c>
-      <c r="U11" s="43" t="s">
-        <v>89</v>
+      <c r="U11" s="42" t="s">
+        <v>76</v>
       </c>
-      <c r="V11" s="43" t="s">
-        <v>90</v>
+      <c r="V11" s="42" t="s">
+        <v>77</v>
       </c>
-      <c r="W11" s="43" t="s">
-        <v>91</v>
+      <c r="W11" s="42" t="s">
+        <v>78</v>
       </c>
-      <c r="X11" s="44">
+      <c r="X11" s="43">
         <v>7</v>
       </c>
-      <c r="Y11" s="44">
+      <c r="Y11" s="43">
         <v>10</v>
       </c>
-      <c r="Z11" s="44">
+      <c r="Z11" s="43">
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="69"/>
-      <c r="AC11" s="44"/>
-      <c r="AD11" s="69"/>
-      <c r="AE11" s="69" t="s">
-        <v>157</v>
+      <c r="AA11" s="43"/>
+      <c r="AB11" s="68"/>
+      <c r="AC11" s="43"/>
+      <c r="AD11" s="68"/>
+      <c r="AE11" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF11" s="70">
+      <c r="AF11" s="69">
         <v>1600006545020</v>
       </c>
-      <c r="AG11" s="69" t="s">
-        <v>159</v>
+      <c r="AG11" s="68" t="s">
+        <v>145</v>
       </c>
-      <c r="AH11" s="45"/>
-      <c r="AI11" s="46" t="str">
+      <c r="AH11" s="44"/>
+      <c r="AI11" s="45" t="str">
         <f t="shared" si="4"/>
         <v>960504601600006545020PASKALIS YUMTE</v>
       </c>
       <c r="AK11" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL11" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -49658,70 +49671,76 @@
       </c>
     </row>
     <row r="12" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="47">
+      <c r="A12" s="46">
         <v>8</v>
       </c>
-      <c r="B12" s="81" t="s">
-        <v>180</v>
+      <c r="B12" s="71" t="s">
+        <v>166</v>
       </c>
-      <c r="C12" s="82" t="s">
-        <v>187</v>
+      <c r="C12" s="72" t="s">
+        <v>173</v>
       </c>
-      <c r="D12" s="83" t="s">
+      <c r="D12" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="82" t="s">
-        <v>192</v>
+      <c r="E12" s="72" t="s">
+        <v>178</v>
       </c>
-      <c r="F12" s="84">
+      <c r="F12" s="74">
         <v>29137</v>
       </c>
       <c r="G12" s="36"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="67"/>
+      <c r="H12" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="I12" s="66"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="38" t="s">
-        <v>151</v>
+      <c r="K12" s="77" t="s">
+        <v>190</v>
       </c>
-      <c r="L12" s="39">
-        <v>2</v>
+      <c r="L12" s="38">
+        <v>0</v>
       </c>
-      <c r="M12" s="39">
-        <v>1</v>
+      <c r="M12" s="38">
+        <v>0</v>
       </c>
-      <c r="N12" s="40"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="44"/>
-      <c r="Y12" s="44"/>
-      <c r="Z12" s="44"/>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="69"/>
-      <c r="AC12" s="44"/>
-      <c r="AD12" s="69"/>
-      <c r="AE12" s="69" t="s">
-        <v>157</v>
+      <c r="N12" s="76" t="s">
+        <v>189</v>
       </c>
-      <c r="AF12" s="70">
+      <c r="O12" s="40"/>
+      <c r="P12" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q12" s="40"/>
+      <c r="R12" s="41"/>
+      <c r="S12" s="41"/>
+      <c r="T12" s="42"/>
+      <c r="U12" s="42"/>
+      <c r="V12" s="42"/>
+      <c r="W12" s="42"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
+      <c r="Z12" s="43"/>
+      <c r="AA12" s="43"/>
+      <c r="AB12" s="68"/>
+      <c r="AC12" s="43"/>
+      <c r="AD12" s="68"/>
+      <c r="AE12" s="68" t="s">
+        <v>143</v>
+      </c>
+      <c r="AF12" s="69">
         <v>1600006544254</v>
       </c>
-      <c r="AG12" s="69" t="s">
-        <v>160</v>
+      <c r="AG12" s="68" t="s">
+        <v>146</v>
       </c>
-      <c r="AH12" s="45"/>
-      <c r="AI12" s="46" t="str">
+      <c r="AH12" s="44"/>
+      <c r="AI12" s="45" t="str">
         <f t="shared" si="4"/>
         <v>960504641600006544254WIHELMUS KORAIN</v>
       </c>
       <c r="AK12" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL12" s="25" t="str">
         <f t="shared" si="0"/>
@@ -49729,64 +49748,66 @@
       </c>
     </row>
     <row r="13" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="47">
+      <c r="A13" s="46">
         <v>9</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D13" s="33"/>
       <c r="E13" s="34"/>
       <c r="F13" s="35"/>
       <c r="G13" s="36"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="67"/>
+      <c r="H13" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="I13" s="66"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="38" t="s">
-        <v>151</v>
+      <c r="K13" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L13" s="39">
+      <c r="L13" s="38">
         <v>2</v>
       </c>
-      <c r="M13" s="39">
+      <c r="M13" s="38">
         <v>1</v>
       </c>
-      <c r="N13" s="40"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="44"/>
-      <c r="Y13" s="44"/>
-      <c r="Z13" s="44"/>
-      <c r="AA13" s="44"/>
-      <c r="AB13" s="69"/>
-      <c r="AC13" s="44"/>
-      <c r="AD13" s="69"/>
-      <c r="AE13" s="69" t="s">
-        <v>157</v>
+      <c r="N13" s="39"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="41"/>
+      <c r="S13" s="41"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="42"/>
+      <c r="V13" s="42"/>
+      <c r="W13" s="42"/>
+      <c r="X13" s="43"/>
+      <c r="Y13" s="43"/>
+      <c r="Z13" s="43"/>
+      <c r="AA13" s="43"/>
+      <c r="AB13" s="68"/>
+      <c r="AC13" s="43"/>
+      <c r="AD13" s="68"/>
+      <c r="AE13" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF13" s="70">
+      <c r="AF13" s="69">
         <v>1600006544262</v>
       </c>
-      <c r="AG13" s="69" t="s">
-        <v>160</v>
+      <c r="AG13" s="68" t="s">
+        <v>146</v>
       </c>
-      <c r="AH13" s="45"/>
-      <c r="AI13" s="46" t="str">
+      <c r="AH13" s="44"/>
+      <c r="AI13" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000091600006544262Nama PB 9</v>
       </c>
       <c r="AK13" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL13" s="25" t="str">
         <f t="shared" si="0"/>
@@ -49794,64 +49815,64 @@
       </c>
     </row>
     <row r="14" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="47">
+      <c r="A14" s="46">
         <v>10</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="D14" s="33"/>
       <c r="E14" s="34"/>
       <c r="F14" s="35"/>
       <c r="G14" s="36"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="67"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="66"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="38" t="s">
-        <v>151</v>
+      <c r="K14" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L14" s="39">
+      <c r="L14" s="38">
         <v>2</v>
       </c>
-      <c r="M14" s="39">
+      <c r="M14" s="38">
         <v>1</v>
       </c>
-      <c r="N14" s="40"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="44"/>
-      <c r="Y14" s="44"/>
-      <c r="Z14" s="44"/>
-      <c r="AA14" s="44"/>
-      <c r="AB14" s="69"/>
-      <c r="AC14" s="44"/>
-      <c r="AD14" s="69"/>
-      <c r="AE14" s="69" t="s">
-        <v>157</v>
+      <c r="N14" s="39"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="41"/>
+      <c r="S14" s="41"/>
+      <c r="T14" s="42"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="42"/>
+      <c r="W14" s="42"/>
+      <c r="X14" s="43"/>
+      <c r="Y14" s="43"/>
+      <c r="Z14" s="43"/>
+      <c r="AA14" s="43"/>
+      <c r="AB14" s="68"/>
+      <c r="AC14" s="43"/>
+      <c r="AD14" s="68"/>
+      <c r="AE14" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF14" s="70">
+      <c r="AF14" s="69">
         <v>1600006544270</v>
       </c>
-      <c r="AG14" s="69" t="s">
-        <v>160</v>
+      <c r="AG14" s="68" t="s">
+        <v>146</v>
       </c>
-      <c r="AH14" s="45"/>
-      <c r="AI14" s="46" t="str">
+      <c r="AH14" s="44"/>
+      <c r="AI14" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000101600006544270Nama PB 10</v>
       </c>
       <c r="AK14" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL14" s="25" t="str">
         <f t="shared" si="0"/>
@@ -49863,20 +49884,20 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="9"/>
       <c r="F15" s="10"/>
       <c r="G15" s="11"/>
       <c r="H15" s="12"/>
-      <c r="I15" s="66"/>
+      <c r="I15" s="65"/>
       <c r="J15" s="13"/>
       <c r="K15" s="14" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="L15" s="15">
         <v>2</v>
@@ -49898,17 +49919,17 @@
       <c r="Y15" s="20"/>
       <c r="Z15" s="20"/>
       <c r="AA15" s="20"/>
-      <c r="AB15" s="68"/>
+      <c r="AB15" s="67"/>
       <c r="AC15" s="20"/>
-      <c r="AD15" s="68"/>
-      <c r="AE15" s="69" t="s">
-        <v>157</v>
+      <c r="AD15" s="67"/>
+      <c r="AE15" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF15" s="71">
+      <c r="AF15" s="70">
         <v>1600006544288</v>
       </c>
-      <c r="AG15" s="69" t="s">
-        <v>160</v>
+      <c r="AG15" s="68" t="s">
+        <v>146</v>
       </c>
       <c r="AH15" s="21"/>
       <c r="AI15" s="22" t="str">
@@ -49916,7 +49937,7 @@
         <v>0000111600006544288Nama PB 11</v>
       </c>
       <c r="AK15" s="23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL15" s="23" t="str">
         <f t="shared" si="0"/>
@@ -49924,64 +49945,64 @@
       </c>
     </row>
     <row r="16" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="47">
+      <c r="A16" s="46">
         <v>12</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="34"/>
       <c r="F16" s="35"/>
       <c r="G16" s="36"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="67"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="66"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="38" t="s">
-        <v>151</v>
+      <c r="K16" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L16" s="39">
+      <c r="L16" s="38">
         <v>2</v>
       </c>
-      <c r="M16" s="39">
+      <c r="M16" s="38">
         <v>1</v>
       </c>
-      <c r="N16" s="40"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="44"/>
-      <c r="Y16" s="44"/>
-      <c r="Z16" s="44"/>
-      <c r="AA16" s="44"/>
-      <c r="AB16" s="69"/>
-      <c r="AC16" s="44"/>
-      <c r="AD16" s="69"/>
-      <c r="AE16" s="69" t="s">
-        <v>157</v>
+      <c r="N16" s="39"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="42"/>
+      <c r="U16" s="42"/>
+      <c r="V16" s="42"/>
+      <c r="W16" s="42"/>
+      <c r="X16" s="43"/>
+      <c r="Y16" s="43"/>
+      <c r="Z16" s="43"/>
+      <c r="AA16" s="43"/>
+      <c r="AB16" s="68"/>
+      <c r="AC16" s="43"/>
+      <c r="AD16" s="68"/>
+      <c r="AE16" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF16" s="70">
+      <c r="AF16" s="69">
         <v>1600006544296</v>
       </c>
-      <c r="AG16" s="69" t="s">
-        <v>160</v>
+      <c r="AG16" s="68" t="s">
+        <v>146</v>
       </c>
-      <c r="AH16" s="45"/>
-      <c r="AI16" s="46" t="str">
+      <c r="AH16" s="44"/>
+      <c r="AI16" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000121600006544296Nama PB 12</v>
       </c>
       <c r="AK16" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL16" s="25" t="str">
         <f t="shared" si="0"/>
@@ -49989,64 +50010,64 @@
       </c>
     </row>
     <row r="17" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="47">
+      <c r="A17" s="46">
         <v>13</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="34"/>
       <c r="F17" s="35"/>
       <c r="G17" s="36"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="67"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="66"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="38" t="s">
-        <v>151</v>
+      <c r="K17" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L17" s="39">
+      <c r="L17" s="38">
         <v>2</v>
       </c>
-      <c r="M17" s="39">
+      <c r="M17" s="38">
         <v>1</v>
       </c>
-      <c r="N17" s="40"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="43"/>
-      <c r="V17" s="43"/>
-      <c r="W17" s="43"/>
-      <c r="X17" s="44"/>
-      <c r="Y17" s="44"/>
-      <c r="Z17" s="44"/>
-      <c r="AA17" s="44"/>
-      <c r="AB17" s="69"/>
-      <c r="AC17" s="44"/>
-      <c r="AD17" s="69"/>
-      <c r="AE17" s="69" t="s">
-        <v>157</v>
+      <c r="N17" s="39"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="40"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="41"/>
+      <c r="T17" s="42"/>
+      <c r="U17" s="42"/>
+      <c r="V17" s="42"/>
+      <c r="W17" s="42"/>
+      <c r="X17" s="43"/>
+      <c r="Y17" s="43"/>
+      <c r="Z17" s="43"/>
+      <c r="AA17" s="43"/>
+      <c r="AB17" s="68"/>
+      <c r="AC17" s="43"/>
+      <c r="AD17" s="68"/>
+      <c r="AE17" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF17" s="70">
+      <c r="AF17" s="69">
         <v>1600006544304</v>
       </c>
-      <c r="AG17" s="69" t="s">
-        <v>160</v>
+      <c r="AG17" s="68" t="s">
+        <v>146</v>
       </c>
-      <c r="AH17" s="45"/>
-      <c r="AI17" s="46" t="str">
+      <c r="AH17" s="44"/>
+      <c r="AI17" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000131600006544304Nama PB 13</v>
       </c>
       <c r="AK17" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL17" s="25" t="str">
         <f t="shared" si="0"/>
@@ -50054,64 +50075,64 @@
       </c>
     </row>
     <row r="18" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="47">
+      <c r="A18" s="46">
         <v>14</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D18" s="33"/>
       <c r="E18" s="34"/>
       <c r="F18" s="35"/>
       <c r="G18" s="36"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="67"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="66"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="38" t="s">
-        <v>151</v>
+      <c r="K18" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L18" s="39">
+      <c r="L18" s="38">
         <v>2</v>
       </c>
-      <c r="M18" s="39">
+      <c r="M18" s="38">
         <v>1</v>
       </c>
-      <c r="N18" s="40"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="43"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="43"/>
-      <c r="X18" s="44"/>
-      <c r="Y18" s="44"/>
-      <c r="Z18" s="44"/>
-      <c r="AA18" s="44"/>
-      <c r="AB18" s="69"/>
-      <c r="AC18" s="44"/>
-      <c r="AD18" s="69"/>
-      <c r="AE18" s="69" t="s">
-        <v>157</v>
+      <c r="N18" s="39"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="40"/>
+      <c r="R18" s="41"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="42"/>
+      <c r="V18" s="42"/>
+      <c r="W18" s="42"/>
+      <c r="X18" s="43"/>
+      <c r="Y18" s="43"/>
+      <c r="Z18" s="43"/>
+      <c r="AA18" s="43"/>
+      <c r="AB18" s="68"/>
+      <c r="AC18" s="43"/>
+      <c r="AD18" s="68"/>
+      <c r="AE18" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF18" s="70">
+      <c r="AF18" s="69">
         <v>1600006544312</v>
       </c>
-      <c r="AG18" s="69" t="s">
-        <v>160</v>
+      <c r="AG18" s="68" t="s">
+        <v>146</v>
       </c>
-      <c r="AH18" s="45"/>
-      <c r="AI18" s="46" t="str">
+      <c r="AH18" s="44"/>
+      <c r="AI18" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000141600006544312Nama PB 14</v>
       </c>
       <c r="AK18" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL18" s="25" t="str">
         <f t="shared" si="0"/>
@@ -50119,64 +50140,64 @@
       </c>
     </row>
     <row r="19" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="47">
+      <c r="A19" s="46">
         <v>15</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D19" s="33"/>
       <c r="E19" s="34"/>
       <c r="F19" s="35"/>
       <c r="G19" s="36"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="67"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="66"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="38" t="s">
-        <v>151</v>
+      <c r="K19" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L19" s="39">
+      <c r="L19" s="38">
         <v>2</v>
       </c>
-      <c r="M19" s="39">
+      <c r="M19" s="38">
         <v>1</v>
       </c>
-      <c r="N19" s="40"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="43"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="43"/>
-      <c r="X19" s="44"/>
-      <c r="Y19" s="44"/>
-      <c r="Z19" s="44"/>
-      <c r="AA19" s="44"/>
-      <c r="AB19" s="69"/>
-      <c r="AC19" s="44"/>
-      <c r="AD19" s="69"/>
-      <c r="AE19" s="69" t="s">
-        <v>157</v>
+      <c r="N19" s="39"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="39"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="42"/>
+      <c r="U19" s="42"/>
+      <c r="V19" s="42"/>
+      <c r="W19" s="42"/>
+      <c r="X19" s="43"/>
+      <c r="Y19" s="43"/>
+      <c r="Z19" s="43"/>
+      <c r="AA19" s="43"/>
+      <c r="AB19" s="68"/>
+      <c r="AC19" s="43"/>
+      <c r="AD19" s="68"/>
+      <c r="AE19" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF19" s="70">
+      <c r="AF19" s="69">
         <v>1600006551267</v>
       </c>
-      <c r="AG19" s="69" t="s">
-        <v>160</v>
+      <c r="AG19" s="68" t="s">
+        <v>146</v>
       </c>
-      <c r="AH19" s="45"/>
-      <c r="AI19" s="46" t="str">
+      <c r="AH19" s="44"/>
+      <c r="AI19" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000151600006551267Nama PB 15</v>
       </c>
       <c r="AK19" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL19" s="25" t="str">
         <f t="shared" si="0"/>
@@ -50184,64 +50205,64 @@
       </c>
     </row>
     <row r="20" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="47">
+      <c r="A20" s="46">
         <v>16</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D20" s="33"/>
       <c r="E20" s="34"/>
       <c r="F20" s="35"/>
       <c r="G20" s="36"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="67"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="66"/>
       <c r="J20" s="4"/>
-      <c r="K20" s="38" t="s">
-        <v>151</v>
+      <c r="K20" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L20" s="39">
+      <c r="L20" s="38">
         <v>2</v>
       </c>
-      <c r="M20" s="39">
+      <c r="M20" s="38">
         <v>1</v>
       </c>
-      <c r="N20" s="40"/>
-      <c r="O20" s="41"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="43"/>
-      <c r="X20" s="44"/>
-      <c r="Y20" s="44"/>
-      <c r="Z20" s="44"/>
-      <c r="AA20" s="44"/>
-      <c r="AB20" s="69"/>
-      <c r="AC20" s="44"/>
-      <c r="AD20" s="69"/>
-      <c r="AE20" s="69" t="s">
-        <v>157</v>
+      <c r="N20" s="39"/>
+      <c r="O20" s="40"/>
+      <c r="P20" s="39"/>
+      <c r="Q20" s="40"/>
+      <c r="R20" s="41"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="42"/>
+      <c r="V20" s="42"/>
+      <c r="W20" s="42"/>
+      <c r="X20" s="43"/>
+      <c r="Y20" s="43"/>
+      <c r="Z20" s="43"/>
+      <c r="AA20" s="43"/>
+      <c r="AB20" s="68"/>
+      <c r="AC20" s="43"/>
+      <c r="AD20" s="68"/>
+      <c r="AE20" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF20" s="70">
+      <c r="AF20" s="69">
         <v>1600006544320</v>
       </c>
-      <c r="AG20" s="69" t="s">
-        <v>160</v>
+      <c r="AG20" s="68" t="s">
+        <v>146</v>
       </c>
-      <c r="AH20" s="45"/>
-      <c r="AI20" s="46" t="str">
+      <c r="AH20" s="44"/>
+      <c r="AI20" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000161600006544320Nama PB 16</v>
       </c>
       <c r="AK20" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL20" s="25" t="str">
         <f t="shared" si="0"/>
@@ -50249,64 +50270,64 @@
       </c>
     </row>
     <row r="21" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="47">
+      <c r="A21" s="46">
         <v>17</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D21" s="33"/>
       <c r="E21" s="34"/>
       <c r="F21" s="35"/>
       <c r="G21" s="36"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="67"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="66"/>
       <c r="J21" s="4"/>
-      <c r="K21" s="38" t="s">
-        <v>151</v>
+      <c r="K21" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L21" s="39">
+      <c r="L21" s="38">
         <v>1</v>
       </c>
-      <c r="M21" s="39">
+      <c r="M21" s="38">
         <v>2</v>
       </c>
-      <c r="N21" s="40"/>
-      <c r="O21" s="41"/>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="42"/>
-      <c r="S21" s="42"/>
-      <c r="T21" s="43"/>
-      <c r="U21" s="43"/>
-      <c r="V21" s="43"/>
-      <c r="W21" s="43"/>
-      <c r="X21" s="44"/>
-      <c r="Y21" s="44"/>
-      <c r="Z21" s="44"/>
-      <c r="AA21" s="44"/>
-      <c r="AB21" s="69"/>
-      <c r="AC21" s="44"/>
-      <c r="AD21" s="69"/>
-      <c r="AE21" s="69" t="s">
-        <v>157</v>
+      <c r="N21" s="39"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="40"/>
+      <c r="R21" s="41"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="42"/>
+      <c r="U21" s="42"/>
+      <c r="V21" s="42"/>
+      <c r="W21" s="42"/>
+      <c r="X21" s="43"/>
+      <c r="Y21" s="43"/>
+      <c r="Z21" s="43"/>
+      <c r="AA21" s="43"/>
+      <c r="AB21" s="68"/>
+      <c r="AC21" s="43"/>
+      <c r="AD21" s="68"/>
+      <c r="AE21" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF21" s="70">
+      <c r="AF21" s="69">
         <v>1600006544346</v>
       </c>
-      <c r="AG21" s="69" t="s">
-        <v>161</v>
+      <c r="AG21" s="68" t="s">
+        <v>147</v>
       </c>
-      <c r="AH21" s="45"/>
-      <c r="AI21" s="46" t="str">
+      <c r="AH21" s="44"/>
+      <c r="AI21" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000171600006544346Nama PB 17</v>
       </c>
       <c r="AK21" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL21" s="25" t="str">
         <f t="shared" si="0"/>
@@ -50314,64 +50335,64 @@
       </c>
     </row>
     <row r="22" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="47">
+      <c r="A22" s="46">
         <v>18</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D22" s="33"/>
       <c r="E22" s="34"/>
       <c r="F22" s="35"/>
       <c r="G22" s="36"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="67"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="66"/>
       <c r="J22" s="4"/>
-      <c r="K22" s="38" t="s">
-        <v>151</v>
+      <c r="K22" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L22" s="39">
+      <c r="L22" s="38">
         <v>1</v>
       </c>
-      <c r="M22" s="39">
+      <c r="M22" s="38">
         <v>2</v>
       </c>
-      <c r="N22" s="40"/>
-      <c r="O22" s="41"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="42"/>
-      <c r="T22" s="43"/>
-      <c r="U22" s="43"/>
-      <c r="V22" s="43"/>
-      <c r="W22" s="43"/>
-      <c r="X22" s="44"/>
-      <c r="Y22" s="44"/>
-      <c r="Z22" s="44"/>
-      <c r="AA22" s="44"/>
-      <c r="AB22" s="69"/>
-      <c r="AC22" s="44"/>
-      <c r="AD22" s="69"/>
-      <c r="AE22" s="69" t="s">
-        <v>157</v>
+      <c r="N22" s="39"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="42"/>
+      <c r="U22" s="42"/>
+      <c r="V22" s="42"/>
+      <c r="W22" s="42"/>
+      <c r="X22" s="43"/>
+      <c r="Y22" s="43"/>
+      <c r="Z22" s="43"/>
+      <c r="AA22" s="43"/>
+      <c r="AB22" s="68"/>
+      <c r="AC22" s="43"/>
+      <c r="AD22" s="68"/>
+      <c r="AE22" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF22" s="70">
+      <c r="AF22" s="69">
         <v>1600006544353</v>
       </c>
-      <c r="AG22" s="69" t="s">
-        <v>161</v>
+      <c r="AG22" s="68" t="s">
+        <v>147</v>
       </c>
-      <c r="AH22" s="45"/>
-      <c r="AI22" s="46" t="str">
+      <c r="AH22" s="44"/>
+      <c r="AI22" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000181600006544353Nama PB 18</v>
       </c>
       <c r="AK22" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL22" s="25" t="str">
         <f t="shared" si="0"/>
@@ -50379,64 +50400,64 @@
       </c>
     </row>
     <row r="23" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="47">
+      <c r="A23" s="46">
         <v>19</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D23" s="33"/>
       <c r="E23" s="34"/>
       <c r="F23" s="35"/>
       <c r="G23" s="36"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="67"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="66"/>
       <c r="J23" s="4"/>
-      <c r="K23" s="38" t="s">
-        <v>151</v>
+      <c r="K23" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L23" s="39">
+      <c r="L23" s="38">
         <v>1</v>
       </c>
-      <c r="M23" s="39">
+      <c r="M23" s="38">
         <v>2</v>
       </c>
-      <c r="N23" s="40"/>
-      <c r="O23" s="41"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="43"/>
-      <c r="U23" s="43"/>
-      <c r="V23" s="43"/>
-      <c r="W23" s="43"/>
-      <c r="X23" s="44"/>
-      <c r="Y23" s="44"/>
-      <c r="Z23" s="44"/>
-      <c r="AA23" s="44"/>
-      <c r="AB23" s="69"/>
-      <c r="AC23" s="44"/>
-      <c r="AD23" s="69"/>
-      <c r="AE23" s="69" t="s">
-        <v>157</v>
+      <c r="N23" s="39"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="41"/>
+      <c r="S23" s="41"/>
+      <c r="T23" s="42"/>
+      <c r="U23" s="42"/>
+      <c r="V23" s="42"/>
+      <c r="W23" s="42"/>
+      <c r="X23" s="43"/>
+      <c r="Y23" s="43"/>
+      <c r="Z23" s="43"/>
+      <c r="AA23" s="43"/>
+      <c r="AB23" s="68"/>
+      <c r="AC23" s="43"/>
+      <c r="AD23" s="68"/>
+      <c r="AE23" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF23" s="70">
+      <c r="AF23" s="69">
         <v>1600006586008</v>
       </c>
-      <c r="AG23" s="69" t="s">
-        <v>161</v>
+      <c r="AG23" s="68" t="s">
+        <v>147</v>
       </c>
-      <c r="AH23" s="45"/>
-      <c r="AI23" s="46" t="str">
+      <c r="AH23" s="44"/>
+      <c r="AI23" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000191600006586008Nama PB 19</v>
       </c>
       <c r="AK23" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL23" s="25" t="str">
         <f t="shared" si="0"/>
@@ -50444,64 +50465,64 @@
       </c>
     </row>
     <row r="24" spans="1:38" s="25" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="47">
+      <c r="A24" s="46">
         <v>20</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D24" s="33"/>
       <c r="E24" s="34"/>
       <c r="F24" s="35"/>
       <c r="G24" s="36"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="67"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="66"/>
       <c r="J24" s="4"/>
-      <c r="K24" s="38" t="s">
-        <v>151</v>
+      <c r="K24" s="37" t="s">
+        <v>138</v>
       </c>
-      <c r="L24" s="39">
+      <c r="L24" s="38">
         <v>1</v>
       </c>
-      <c r="M24" s="39">
+      <c r="M24" s="38">
         <v>2</v>
       </c>
-      <c r="N24" s="40"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="42"/>
-      <c r="S24" s="42"/>
-      <c r="T24" s="43"/>
-      <c r="U24" s="43"/>
-      <c r="V24" s="43"/>
-      <c r="W24" s="43"/>
-      <c r="X24" s="44"/>
-      <c r="Y24" s="44"/>
-      <c r="Z24" s="44"/>
-      <c r="AA24" s="44"/>
-      <c r="AB24" s="69"/>
-      <c r="AC24" s="44"/>
-      <c r="AD24" s="69"/>
-      <c r="AE24" s="69" t="s">
-        <v>157</v>
+      <c r="N24" s="39"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="39"/>
+      <c r="Q24" s="40"/>
+      <c r="R24" s="41"/>
+      <c r="S24" s="41"/>
+      <c r="T24" s="42"/>
+      <c r="U24" s="42"/>
+      <c r="V24" s="42"/>
+      <c r="W24" s="42"/>
+      <c r="X24" s="43"/>
+      <c r="Y24" s="43"/>
+      <c r="Z24" s="43"/>
+      <c r="AA24" s="43"/>
+      <c r="AB24" s="68"/>
+      <c r="AC24" s="43"/>
+      <c r="AD24" s="68"/>
+      <c r="AE24" s="68" t="s">
+        <v>143</v>
       </c>
-      <c r="AF24" s="70">
+      <c r="AF24" s="69">
         <v>1600006544361</v>
       </c>
-      <c r="AG24" s="69" t="s">
-        <v>161</v>
+      <c r="AG24" s="68" t="s">
+        <v>147</v>
       </c>
-      <c r="AH24" s="45"/>
-      <c r="AI24" s="46" t="str">
+      <c r="AH24" s="44"/>
+      <c r="AI24" s="45" t="str">
         <f t="shared" si="4"/>
         <v>0000201600006544361Nama PB 20</v>
       </c>
       <c r="AK24" s="25" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AL24" s="25" t="str">
         <f t="shared" si="0"/>
@@ -50510,95 +50531,115 @@
     </row>
     <row r="25" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="I26" s="50" t="s">
-        <v>93</v>
+      <c r="I26" s="49" t="s">
+        <v>80</v>
       </c>
-      <c r="J26" s="49" t="s">
-        <v>92</v>
+      <c r="J26" s="48" t="s">
+        <v>79</v>
       </c>
-      <c r="N26" s="50" t="s">
-        <v>93</v>
+      <c r="N26" s="49" t="s">
+        <v>80</v>
       </c>
-      <c r="O26" s="51"/>
-      <c r="P26" s="50" t="s">
-        <v>93</v>
+      <c r="O26" s="50"/>
+      <c r="P26" s="49" t="s">
+        <v>80</v>
       </c>
-      <c r="R26" s="49" t="s">
-        <v>94</v>
+      <c r="R26" s="48" t="s">
+        <v>81</v>
       </c>
-      <c r="AF26" s="50" t="s">
-        <v>93</v>
+      <c r="AF26" s="49" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="52" t="s">
-        <v>95</v>
+      <c r="B27" s="51" t="s">
+        <v>82</v>
       </c>
-      <c r="C27" s="53" t="s">
-        <v>152</v>
+      <c r="C27" s="52" t="s">
+        <v>191</v>
       </c>
-      <c r="D27" s="80" t="s">
-        <v>96</v>
+      <c r="D27" s="84" t="s">
+        <v>83</v>
       </c>
-      <c r="E27" s="80"/>
-      <c r="J27" s="49" t="s">
-        <v>97</v>
+      <c r="E27" s="84"/>
+      <c r="J27" s="48" t="s">
+        <v>84</v>
       </c>
-      <c r="R27" s="42">
+      <c r="R27" s="41">
         <v>-7.4668999999999999</v>
       </c>
-      <c r="S27" s="42">
+      <c r="S27" s="41">
         <v>109.5536</v>
       </c>
     </row>
     <row r="28" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="52" t="s">
-        <v>98</v>
+      <c r="B28" s="51" t="s">
+        <v>85</v>
       </c>
-      <c r="C28" s="54" t="str">
+      <c r="C28" s="53" t="str">
         <f>VLOOKUP(D28,$A$2:$C$24,3,FALSE)</f>
-        <v xml:space="preserve">AGNES ASSEM </v>
+        <v>APOLONIA KORAIN</v>
       </c>
-      <c r="D28" s="78">
-        <v>1</v>
+      <c r="D28" s="83">
+        <v>3</v>
       </c>
-      <c r="E28" s="78"/>
+      <c r="E28" s="83"/>
     </row>
     <row r="29" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="52" t="s">
-        <v>99</v>
+      <c r="B29" s="51" t="s">
+        <v>86</v>
       </c>
-      <c r="C29" s="54" t="str">
+      <c r="C29" s="53" t="str">
         <f>VLOOKUP(D29,$A$2:$C$24,3,FALSE)</f>
-        <v>BARTOLOMEUS KORAIN</v>
+        <v>APOLONIA KORAIN</v>
       </c>
-      <c r="D29" s="78">
-        <v>4</v>
+      <c r="D29" s="83">
+        <v>3</v>
       </c>
-      <c r="E29" s="78"/>
+      <c r="E29" s="83"/>
     </row>
     <row r="30" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="52" t="s">
-        <v>100</v>
+      <c r="B30" s="51" t="s">
+        <v>87</v>
       </c>
-      <c r="C30" s="54" t="str">
+      <c r="C30" s="53" t="str">
         <f>VLOOKUP(D30,$A$2:$C$24,3,FALSE)</f>
-        <v>MONICA KORAIN</v>
+        <v>MATILDA TAA</v>
       </c>
-      <c r="D30" s="78">
-        <v>6</v>
+      <c r="D30" s="83">
+        <v>5</v>
       </c>
-      <c r="E30" s="78"/>
+      <c r="E30" s="83"/>
     </row>
     <row r="31" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="10:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J33" s="55"/>
+      <c r="J33" s="54"/>
     </row>
     <row r="34" spans="10:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="10:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="AE2:AE4"/>
+    <mergeCell ref="AF2:AF4"/>
+    <mergeCell ref="AA2:AA4"/>
+    <mergeCell ref="AB2:AB4"/>
+    <mergeCell ref="AC2:AC4"/>
+    <mergeCell ref="AD2:AD4"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="O2:O4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
     <mergeCell ref="AG2:AG4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
@@ -50615,67 +50656,47 @@
     <mergeCell ref="R2:S4"/>
     <mergeCell ref="T2:W2"/>
     <mergeCell ref="J2:J4"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="O2:O4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="AE2:AE4"/>
-    <mergeCell ref="AF2:AF4"/>
-    <mergeCell ref="AA2:AA4"/>
-    <mergeCell ref="AB2:AB4"/>
-    <mergeCell ref="AC2:AC4"/>
-    <mergeCell ref="AD2:AD4"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <conditionalFormatting sqref="C5:C24">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N5:N24">
-    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N15:N24">
-    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22:N24">
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P24">
-    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P15:P24">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P22:P24">
-    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="NO KK" sqref="P5:P24" xr:uid="{2FF7C5AD-0759-3641-A164-C0AE401DB8AD}">
